--- a/templates/trip_template.xlsx
+++ b/templates/trip_template.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parrottkim/Projects/javascript/taskflow-backend/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F24930C-2D0F-D749-A481-553BB3E15468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509DD080-CC15-C944-BD15-3EF7955ED852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="21100" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18340" yWindow="500" windowWidth="32460" windowHeight="20700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic" sheetId="1" r:id="rId1"/>
     <sheet name="Overseas" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Domestic!$A$1:$L$53</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -202,7 +205,6 @@
         <sz val="14"/>
         <color theme="1"/>
         <rFont val="Pretendard"/>
-        <charset val="1"/>
       </rPr>
       <t>개인차량 유류비</t>
     </r>
@@ -370,60 +372,50 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="48"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF0000FF"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="0"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -436,20 +428,17 @@
       <b/>
       <sz val="12"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Pretendard"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1234,30 +1223,120 @@
     <xf numFmtId="189" fontId="4" fillId="6" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="15" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="6" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="6" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1276,176 +1355,86 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="5" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="6" fillId="6" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="4" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="6" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="6" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="5" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="5" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="5" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="5" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="6" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="6" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="5" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="6" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="6" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="6" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="15" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1809,9 +1798,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
@@ -1826,17 +1812,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="83" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="85" t="s">
         <v>1</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -1851,34 +1837,34 @@
       <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" ht="120" customHeight="1">
-      <c r="A2" s="82"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="83"/>
+      <c r="A2" s="126"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="85"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="6"/>
       <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="86" t="s">
+      <c r="B3" s="119"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="86"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="83"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="85"/>
       <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
@@ -1890,198 +1876,198 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A4" s="87" t="s">
+      <c r="A4" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="86" t="s">
+      <c r="B4" s="115"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="86"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="91" t="s">
+      <c r="B5" s="119"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="91"/>
-      <c r="H5" s="92" t="s">
+      <c r="G5" s="121"/>
+      <c r="H5" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="92"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
     </row>
     <row r="6" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A6" s="84"/>
-      <c r="B6" s="84"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="94"/>
+      <c r="A6" s="119"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
       <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="11"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="123"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="123"/>
     </row>
     <row r="7" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A7" s="84"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
+      <c r="A7" s="119"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="123"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="123"/>
     </row>
     <row r="8" spans="1:13" ht="7.5" customHeight="1">
       <c r="A8" s="12"/>
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A9" s="96" t="s">
+      <c r="A9" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
+      <c r="B9" s="107"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="107"/>
     </row>
     <row r="10" spans="1:13" ht="18" customHeight="1">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
-      <c r="F10" s="97"/>
-      <c r="G10" s="97"/>
-      <c r="H10" s="97"/>
-      <c r="I10" s="97"/>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
+      <c r="B10" s="108"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
     </row>
     <row r="11" spans="1:13" ht="18" customHeight="1">
-      <c r="A11" s="98" t="s">
+      <c r="A11" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="98"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="109"/>
+      <c r="D11" s="109"/>
+      <c r="E11" s="109"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="109"/>
+      <c r="J11" s="109"/>
+      <c r="K11" s="109"/>
+      <c r="L11" s="109"/>
     </row>
     <row r="12" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A12" s="99"/>
-      <c r="B12" s="99"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="99"/>
-      <c r="L12" s="99"/>
+      <c r="A12" s="151"/>
+      <c r="B12" s="151"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="151"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="151"/>
+      <c r="K12" s="151"/>
+      <c r="L12" s="151"/>
     </row>
     <row r="13" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A13" s="99"/>
-      <c r="B13" s="99"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="99"/>
-      <c r="J13" s="99"/>
-      <c r="K13" s="99"/>
-      <c r="L13" s="99"/>
+      <c r="A13" s="151"/>
+      <c r="B13" s="151"/>
+      <c r="C13" s="151"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="151"/>
+      <c r="F13" s="151"/>
+      <c r="G13" s="151"/>
+      <c r="H13" s="151"/>
+      <c r="I13" s="151"/>
+      <c r="J13" s="151"/>
+      <c r="K13" s="151"/>
+      <c r="L13" s="151"/>
     </row>
     <row r="14" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A14" s="99"/>
-      <c r="B14" s="99"/>
-      <c r="C14" s="99"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="99"/>
-      <c r="G14" s="99"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="99"/>
-      <c r="K14" s="99"/>
-      <c r="L14" s="99"/>
+      <c r="A14" s="151"/>
+      <c r="B14" s="151"/>
+      <c r="C14" s="151"/>
+      <c r="D14" s="151"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="151"/>
+      <c r="G14" s="151"/>
+      <c r="H14" s="151"/>
+      <c r="I14" s="151"/>
+      <c r="J14" s="151"/>
+      <c r="K14" s="151"/>
+      <c r="L14" s="151"/>
     </row>
     <row r="15" spans="1:13" ht="7.5" customHeight="1">
       <c r="A15" s="12"/>
       <c r="L15" s="13"/>
     </row>
     <row r="16" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="100"/>
-      <c r="C16" s="101" t="s">
+      <c r="B16" s="152"/>
+      <c r="C16" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="101"/>
-      <c r="H16" s="102" t="s">
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="102"/>
-      <c r="J16" s="102"/>
-      <c r="K16" s="102"/>
-      <c r="L16" s="102"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="113"/>
     </row>
     <row r="17" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A17" s="100"/>
-      <c r="B17" s="100"/>
-      <c r="C17" s="103" t="s">
+      <c r="A17" s="152"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="103"/>
+      <c r="D17" s="111"/>
       <c r="E17" s="16" t="s">
         <v>21</v>
       </c>
@@ -2094,76 +2080,76 @@
       <c r="H17" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="104" t="s">
+      <c r="I17" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="104"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="104"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="114"/>
     </row>
     <row r="18" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A18" s="105" t="s">
+      <c r="A18" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="105"/>
-      <c r="C18" s="106" t="s">
+      <c r="B18" s="145"/>
+      <c r="C18" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="106"/>
+      <c r="D18" s="95"/>
       <c r="E18" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F18" s="19"/>
       <c r="G18" s="20"/>
       <c r="H18" s="21"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="107"/>
-      <c r="K18" s="107"/>
-      <c r="L18" s="107"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="135"/>
+      <c r="L18" s="135"/>
     </row>
     <row r="19" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A19" s="105"/>
-      <c r="B19" s="105"/>
-      <c r="C19" s="106" t="s">
+      <c r="A19" s="145"/>
+      <c r="B19" s="145"/>
+      <c r="C19" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="106"/>
+      <c r="D19" s="95"/>
       <c r="E19" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
       <c r="H19" s="21"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="107"/>
+      <c r="I19" s="135"/>
+      <c r="J19" s="135"/>
+      <c r="K19" s="135"/>
+      <c r="L19" s="135"/>
     </row>
     <row r="20" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A20" s="105"/>
-      <c r="B20" s="105"/>
-      <c r="C20" s="106" t="s">
+      <c r="A20" s="145"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="106"/>
+      <c r="D20" s="95"/>
       <c r="E20" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
       <c r="H20" s="21"/>
-      <c r="I20" s="107"/>
-      <c r="J20" s="107"/>
-      <c r="K20" s="107"/>
-      <c r="L20" s="107"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="135"/>
+      <c r="K20" s="135"/>
+      <c r="L20" s="135"/>
     </row>
     <row r="21" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A21" s="105"/>
-      <c r="B21" s="105"/>
-      <c r="C21" s="108" t="s">
+      <c r="A21" s="145"/>
+      <c r="B21" s="145"/>
+      <c r="C21" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="108"/>
+      <c r="D21" s="91"/>
       <c r="E21" s="22"/>
       <c r="F21" s="23"/>
       <c r="G21" s="24"/>
@@ -2171,74 +2157,74 @@
         <f>SUM(H18:H20)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
+      <c r="I21" s="141"/>
+      <c r="J21" s="141"/>
+      <c r="K21" s="141"/>
+      <c r="L21" s="141"/>
     </row>
     <row r="22" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A22" s="110" t="s">
+      <c r="A22" s="134" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="110"/>
-      <c r="C22" s="111" t="s">
+      <c r="B22" s="134"/>
+      <c r="C22" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="111"/>
+      <c r="D22" s="88"/>
       <c r="E22" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="26"/>
       <c r="G22" s="27"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="107"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="107"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="135"/>
+      <c r="K22" s="135"/>
+      <c r="L22" s="135"/>
     </row>
     <row r="23" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A23" s="110"/>
-      <c r="B23" s="110"/>
-      <c r="C23" s="111" t="s">
+      <c r="A23" s="134"/>
+      <c r="B23" s="134"/>
+      <c r="C23" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="111"/>
+      <c r="D23" s="88"/>
       <c r="E23" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F23" s="26"/>
       <c r="G23" s="27"/>
       <c r="H23" s="28"/>
-      <c r="I23" s="112"/>
-      <c r="J23" s="112"/>
-      <c r="K23" s="112"/>
-      <c r="L23" s="112"/>
+      <c r="I23" s="150"/>
+      <c r="J23" s="150"/>
+      <c r="K23" s="150"/>
+      <c r="L23" s="150"/>
     </row>
     <row r="24" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A24" s="110"/>
-      <c r="B24" s="110"/>
-      <c r="C24" s="111" t="s">
+      <c r="A24" s="134"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="111"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F24" s="26"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28"/>
-      <c r="I24" s="112"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="112"/>
-      <c r="L24" s="112"/>
+      <c r="I24" s="150"/>
+      <c r="J24" s="150"/>
+      <c r="K24" s="150"/>
+      <c r="L24" s="150"/>
     </row>
     <row r="25" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A25" s="110"/>
-      <c r="B25" s="110"/>
-      <c r="C25" s="108" t="s">
+      <c r="A25" s="134"/>
+      <c r="B25" s="134"/>
+      <c r="C25" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="108"/>
+      <c r="D25" s="91"/>
       <c r="E25" s="22"/>
       <c r="F25" s="23"/>
       <c r="G25" s="24"/>
@@ -2246,20 +2232,20 @@
         <f>SUM(H22:H24)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="109"/>
-      <c r="J25" s="109"/>
-      <c r="K25" s="109"/>
-      <c r="L25" s="109"/>
+      <c r="I25" s="141"/>
+      <c r="J25" s="141"/>
+      <c r="K25" s="141"/>
+      <c r="L25" s="141"/>
     </row>
     <row r="26" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A26" s="105" t="s">
+      <c r="A26" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="105"/>
-      <c r="C26" s="106" t="s">
+      <c r="B26" s="145"/>
+      <c r="C26" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="106"/>
+      <c r="D26" s="95"/>
       <c r="E26" s="17">
         <v>70000</v>
       </c>
@@ -2271,18 +2257,18 @@
         <v>0</v>
       </c>
       <c r="H26" s="21"/>
-      <c r="I26" s="107"/>
-      <c r="J26" s="107"/>
-      <c r="K26" s="107"/>
-      <c r="L26" s="107"/>
+      <c r="I26" s="135"/>
+      <c r="J26" s="135"/>
+      <c r="K26" s="135"/>
+      <c r="L26" s="135"/>
     </row>
     <row r="27" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A27" s="105"/>
-      <c r="B27" s="105"/>
-      <c r="C27" s="106" t="s">
+      <c r="A27" s="145"/>
+      <c r="B27" s="145"/>
+      <c r="C27" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="106"/>
+      <c r="D27" s="95"/>
       <c r="E27" s="17">
         <v>60000</v>
       </c>
@@ -2294,18 +2280,18 @@
         <v>0</v>
       </c>
       <c r="H27" s="21"/>
-      <c r="I27" s="107"/>
-      <c r="J27" s="107"/>
-      <c r="K27" s="107"/>
-      <c r="L27" s="107"/>
+      <c r="I27" s="135"/>
+      <c r="J27" s="135"/>
+      <c r="K27" s="135"/>
+      <c r="L27" s="135"/>
     </row>
     <row r="28" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A28" s="105"/>
-      <c r="B28" s="105"/>
-      <c r="C28" s="106" t="s">
+      <c r="A28" s="145"/>
+      <c r="B28" s="145"/>
+      <c r="C28" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="106"/>
+      <c r="D28" s="95"/>
       <c r="E28" s="17">
         <v>50000</v>
       </c>
@@ -2317,18 +2303,18 @@
         <v>0</v>
       </c>
       <c r="H28" s="21"/>
-      <c r="I28" s="107"/>
-      <c r="J28" s="107"/>
-      <c r="K28" s="107"/>
-      <c r="L28" s="107"/>
+      <c r="I28" s="135"/>
+      <c r="J28" s="135"/>
+      <c r="K28" s="135"/>
+      <c r="L28" s="135"/>
     </row>
     <row r="29" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A29" s="105"/>
-      <c r="B29" s="105"/>
-      <c r="C29" s="108" t="s">
+      <c r="A29" s="145"/>
+      <c r="B29" s="145"/>
+      <c r="C29" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="108"/>
+      <c r="D29" s="91"/>
       <c r="E29" s="22"/>
       <c r="F29" s="23"/>
       <c r="G29" s="24">
@@ -2339,18 +2325,18 @@
         <f>SUM(H26:H28)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="109"/>
-      <c r="J29" s="109"/>
-      <c r="K29" s="109"/>
-      <c r="L29" s="109"/>
+      <c r="I29" s="141"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="141"/>
+      <c r="L29" s="141"/>
     </row>
     <row r="30" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A30" s="105"/>
-      <c r="B30" s="105"/>
-      <c r="C30" s="113" t="s">
+      <c r="A30" s="145"/>
+      <c r="B30" s="145"/>
+      <c r="C30" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="113"/>
+      <c r="D30" s="146"/>
       <c r="E30" s="29"/>
       <c r="F30" s="30"/>
       <c r="G30" s="31"/>
@@ -2358,90 +2344,90 @@
         <f>G29-H29</f>
         <v>0</v>
       </c>
-      <c r="I30" s="114" t="s">
+      <c r="I30" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="114"/>
-      <c r="K30" s="114"/>
-      <c r="L30" s="114"/>
+      <c r="J30" s="147"/>
+      <c r="K30" s="147"/>
+      <c r="L30" s="147"/>
     </row>
     <row r="31" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A31" s="105"/>
-      <c r="B31" s="105"/>
-      <c r="C31" s="115" t="s">
+      <c r="A31" s="145"/>
+      <c r="B31" s="145"/>
+      <c r="C31" s="148" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="115"/>
-      <c r="G31" s="115"/>
+      <c r="D31" s="148"/>
+      <c r="E31" s="148"/>
+      <c r="F31" s="148"/>
+      <c r="G31" s="148"/>
       <c r="H31" s="33"/>
-      <c r="I31" s="116"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="116"/>
-      <c r="L31" s="116"/>
+      <c r="I31" s="149"/>
+      <c r="J31" s="149"/>
+      <c r="K31" s="149"/>
+      <c r="L31" s="149"/>
     </row>
     <row r="32" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A32" s="105"/>
-      <c r="B32" s="105"/>
-      <c r="C32" s="115" t="s">
+      <c r="A32" s="145"/>
+      <c r="B32" s="145"/>
+      <c r="C32" s="148" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="115"/>
-      <c r="E32" s="115"/>
-      <c r="F32" s="115"/>
-      <c r="G32" s="115"/>
+      <c r="D32" s="148"/>
+      <c r="E32" s="148"/>
+      <c r="F32" s="148"/>
+      <c r="G32" s="148"/>
       <c r="H32" s="33"/>
-      <c r="I32" s="116"/>
-      <c r="J32" s="116"/>
-      <c r="K32" s="116"/>
-      <c r="L32" s="116"/>
+      <c r="I32" s="149"/>
+      <c r="J32" s="149"/>
+      <c r="K32" s="149"/>
+      <c r="L32" s="149"/>
     </row>
     <row r="33" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A33" s="117" t="s">
+      <c r="A33" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="117"/>
-      <c r="C33" s="111" t="s">
+      <c r="B33" s="142"/>
+      <c r="C33" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="111"/>
+      <c r="D33" s="88"/>
       <c r="E33" s="17">
         <v>35000</v>
       </c>
       <c r="F33" s="26"/>
       <c r="G33" s="34"/>
       <c r="H33" s="21"/>
-      <c r="I33" s="107"/>
-      <c r="J33" s="107"/>
-      <c r="K33" s="107"/>
-      <c r="L33" s="107"/>
+      <c r="I33" s="135"/>
+      <c r="J33" s="135"/>
+      <c r="K33" s="135"/>
+      <c r="L33" s="135"/>
     </row>
     <row r="34" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A34" s="117"/>
-      <c r="B34" s="117"/>
-      <c r="C34" s="111" t="s">
+      <c r="A34" s="142"/>
+      <c r="B34" s="142"/>
+      <c r="C34" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="111"/>
+      <c r="D34" s="88"/>
       <c r="E34" s="17">
         <v>30000</v>
       </c>
       <c r="F34" s="26"/>
       <c r="G34" s="34"/>
       <c r="H34" s="21"/>
-      <c r="I34" s="107"/>
-      <c r="J34" s="107"/>
-      <c r="K34" s="107"/>
-      <c r="L34" s="107"/>
+      <c r="I34" s="135"/>
+      <c r="J34" s="135"/>
+      <c r="K34" s="135"/>
+      <c r="L34" s="135"/>
     </row>
     <row r="35" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A35" s="117"/>
-      <c r="B35" s="117"/>
-      <c r="C35" s="118" t="s">
+      <c r="A35" s="142"/>
+      <c r="B35" s="142"/>
+      <c r="C35" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="118"/>
+      <c r="D35" s="143"/>
       <c r="E35" s="35"/>
       <c r="F35" s="36"/>
       <c r="G35" s="36"/>
@@ -2449,90 +2435,90 @@
         <f>SUM(H33:H34)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="119"/>
-      <c r="J35" s="119"/>
-      <c r="K35" s="119"/>
-      <c r="L35" s="119"/>
+      <c r="I35" s="144"/>
+      <c r="J35" s="144"/>
+      <c r="K35" s="144"/>
+      <c r="L35" s="144"/>
     </row>
     <row r="36" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A36" s="117"/>
-      <c r="B36" s="117"/>
-      <c r="C36" s="120" t="s">
+      <c r="A36" s="142"/>
+      <c r="B36" s="142"/>
+      <c r="C36" s="137" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="120"/>
-      <c r="E36" s="120"/>
-      <c r="F36" s="120"/>
-      <c r="G36" s="120"/>
+      <c r="D36" s="137"/>
+      <c r="E36" s="137"/>
+      <c r="F36" s="137"/>
+      <c r="G36" s="137"/>
       <c r="H36" s="21"/>
-      <c r="I36" s="107"/>
-      <c r="J36" s="107"/>
-      <c r="K36" s="107"/>
-      <c r="L36" s="107"/>
+      <c r="I36" s="135"/>
+      <c r="J36" s="135"/>
+      <c r="K36" s="135"/>
+      <c r="L36" s="135"/>
     </row>
     <row r="37" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A37" s="117"/>
-      <c r="B37" s="117"/>
-      <c r="C37" s="121" t="s">
+      <c r="A37" s="142"/>
+      <c r="B37" s="142"/>
+      <c r="C37" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="121"/>
-      <c r="E37" s="121"/>
-      <c r="F37" s="121"/>
-      <c r="G37" s="121"/>
+      <c r="D37" s="139"/>
+      <c r="E37" s="139"/>
+      <c r="F37" s="139"/>
+      <c r="G37" s="139"/>
       <c r="H37" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="I37" s="122"/>
-      <c r="J37" s="122"/>
-      <c r="K37" s="122"/>
-      <c r="L37" s="122"/>
+      <c r="I37" s="140"/>
+      <c r="J37" s="140"/>
+      <c r="K37" s="140"/>
+      <c r="L37" s="140"/>
     </row>
     <row r="38" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A38" s="110" t="s">
+      <c r="A38" s="134" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="110"/>
-      <c r="C38" s="111" t="s">
+      <c r="B38" s="134"/>
+      <c r="C38" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="D38" s="111"/>
+      <c r="D38" s="88"/>
       <c r="E38" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F38" s="26"/>
       <c r="G38" s="27"/>
       <c r="H38" s="21"/>
-      <c r="I38" s="107"/>
-      <c r="J38" s="107"/>
-      <c r="K38" s="107"/>
-      <c r="L38" s="107"/>
+      <c r="I38" s="135"/>
+      <c r="J38" s="135"/>
+      <c r="K38" s="135"/>
+      <c r="L38" s="135"/>
     </row>
     <row r="39" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A39" s="110"/>
-      <c r="B39" s="110"/>
-      <c r="C39" s="111" t="s">
+      <c r="A39" s="134"/>
+      <c r="B39" s="134"/>
+      <c r="C39" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="D39" s="111"/>
+      <c r="D39" s="88"/>
       <c r="E39" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F39" s="26"/>
       <c r="G39" s="27"/>
       <c r="H39" s="21"/>
-      <c r="I39" s="107"/>
-      <c r="J39" s="107"/>
-      <c r="K39" s="107"/>
-      <c r="L39" s="107"/>
+      <c r="I39" s="135"/>
+      <c r="J39" s="135"/>
+      <c r="K39" s="135"/>
+      <c r="L39" s="135"/>
     </row>
     <row r="40" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A40" s="110"/>
-      <c r="B40" s="110"/>
-      <c r="C40" s="123" t="s">
+      <c r="A40" s="134"/>
+      <c r="B40" s="134"/>
+      <c r="C40" s="136" t="s">
         <v>52</v>
       </c>
-      <c r="D40" s="123"/>
+      <c r="D40" s="136"/>
       <c r="E40" s="39" t="s">
         <v>53</v>
       </c>
@@ -2543,82 +2529,82 @@
         <v>55</v>
       </c>
       <c r="H40" s="21"/>
-      <c r="I40" s="107"/>
-      <c r="J40" s="107"/>
-      <c r="K40" s="107"/>
-      <c r="L40" s="107"/>
+      <c r="I40" s="135"/>
+      <c r="J40" s="135"/>
+      <c r="K40" s="135"/>
+      <c r="L40" s="135"/>
     </row>
     <row r="41" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A41" s="110"/>
-      <c r="B41" s="110"/>
-      <c r="C41" s="123"/>
-      <c r="D41" s="123"/>
+      <c r="A41" s="134"/>
+      <c r="B41" s="134"/>
+      <c r="C41" s="136"/>
+      <c r="D41" s="136"/>
       <c r="E41" s="17"/>
       <c r="F41" s="26"/>
       <c r="G41" s="27"/>
       <c r="H41" s="21"/>
-      <c r="I41" s="107"/>
-      <c r="J41" s="107"/>
-      <c r="K41" s="107"/>
-      <c r="L41" s="107"/>
+      <c r="I41" s="135"/>
+      <c r="J41" s="135"/>
+      <c r="K41" s="135"/>
+      <c r="L41" s="135"/>
     </row>
     <row r="42" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A42" s="110"/>
-      <c r="B42" s="110"/>
-      <c r="C42" s="120" t="s">
+      <c r="A42" s="134"/>
+      <c r="B42" s="134"/>
+      <c r="C42" s="137" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="120"/>
-      <c r="E42" s="120"/>
-      <c r="F42" s="120"/>
-      <c r="G42" s="120"/>
+      <c r="D42" s="137"/>
+      <c r="E42" s="137"/>
+      <c r="F42" s="137"/>
+      <c r="G42" s="137"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="124"/>
-      <c r="J42" s="124"/>
-      <c r="K42" s="124"/>
-      <c r="L42" s="124"/>
+      <c r="I42" s="138"/>
+      <c r="J42" s="138"/>
+      <c r="K42" s="138"/>
+      <c r="L42" s="138"/>
     </row>
     <row r="43" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A43" s="110"/>
-      <c r="B43" s="110"/>
-      <c r="C43" s="121" t="s">
+      <c r="A43" s="134"/>
+      <c r="B43" s="134"/>
+      <c r="C43" s="139" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="121"/>
-      <c r="E43" s="121"/>
-      <c r="F43" s="121"/>
-      <c r="G43" s="121"/>
+      <c r="D43" s="139"/>
+      <c r="E43" s="139"/>
+      <c r="F43" s="139"/>
+      <c r="G43" s="139"/>
       <c r="H43" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="I43" s="122"/>
-      <c r="J43" s="122"/>
-      <c r="K43" s="122"/>
-      <c r="L43" s="122"/>
+      <c r="I43" s="140"/>
+      <c r="J43" s="140"/>
+      <c r="K43" s="140"/>
+      <c r="L43" s="140"/>
     </row>
     <row r="44" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A44" s="110"/>
-      <c r="B44" s="110"/>
-      <c r="C44" s="120" t="s">
+      <c r="A44" s="134"/>
+      <c r="B44" s="134"/>
+      <c r="C44" s="137" t="s">
         <v>58</v>
       </c>
-      <c r="D44" s="120"/>
-      <c r="E44" s="120"/>
-      <c r="F44" s="120"/>
-      <c r="G44" s="120"/>
+      <c r="D44" s="137"/>
+      <c r="E44" s="137"/>
+      <c r="F44" s="137"/>
+      <c r="G44" s="137"/>
       <c r="H44" s="42"/>
-      <c r="I44" s="124"/>
-      <c r="J44" s="124"/>
-      <c r="K44" s="124"/>
-      <c r="L44" s="124"/>
+      <c r="I44" s="138"/>
+      <c r="J44" s="138"/>
+      <c r="K44" s="138"/>
+      <c r="L44" s="138"/>
     </row>
     <row r="45" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A45" s="110"/>
-      <c r="B45" s="110"/>
-      <c r="C45" s="108" t="s">
+      <c r="A45" s="134"/>
+      <c r="B45" s="134"/>
+      <c r="C45" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="D45" s="108"/>
+      <c r="D45" s="91"/>
       <c r="E45" s="22"/>
       <c r="F45" s="23"/>
       <c r="G45" s="24"/>
@@ -2626,73 +2612,73 @@
         <f>SUM(H38:H44)</f>
         <v>0</v>
       </c>
-      <c r="I45" s="109"/>
-      <c r="J45" s="109"/>
-      <c r="K45" s="109"/>
-      <c r="L45" s="109"/>
+      <c r="I45" s="141"/>
+      <c r="J45" s="141"/>
+      <c r="K45" s="141"/>
+      <c r="L45" s="141"/>
     </row>
     <row r="46" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A46" s="126" t="s">
+      <c r="A46" s="128" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="126"/>
-      <c r="C46" s="127" t="s">
+      <c r="B46" s="128"/>
+      <c r="C46" s="129" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="127"/>
-      <c r="E46" s="127"/>
-      <c r="F46" s="127"/>
-      <c r="G46" s="127"/>
+      <c r="D46" s="129"/>
+      <c r="E46" s="129"/>
+      <c r="F46" s="129"/>
+      <c r="G46" s="129"/>
       <c r="H46" s="44">
         <f>H21+H25+G29+G35+H45</f>
         <v>0</v>
       </c>
-      <c r="I46" s="128"/>
-      <c r="J46" s="128"/>
-      <c r="K46" s="128"/>
-      <c r="L46" s="128"/>
+      <c r="I46" s="130"/>
+      <c r="J46" s="130"/>
+      <c r="K46" s="130"/>
+      <c r="L46" s="130"/>
     </row>
     <row r="47" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A47" s="126"/>
-      <c r="B47" s="126"/>
-      <c r="C47" s="129" t="s">
+      <c r="A47" s="128"/>
+      <c r="B47" s="128"/>
+      <c r="C47" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="129"/>
-      <c r="E47" s="129"/>
-      <c r="F47" s="129"/>
-      <c r="G47" s="129"/>
+      <c r="D47" s="131"/>
+      <c r="E47" s="131"/>
+      <c r="F47" s="131"/>
+      <c r="G47" s="131"/>
       <c r="H47" s="45">
         <f>H30</f>
         <v>0</v>
       </c>
-      <c r="I47" s="130" t="s">
+      <c r="I47" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="J47" s="130"/>
-      <c r="K47" s="130"/>
-      <c r="L47" s="130"/>
+      <c r="J47" s="132"/>
+      <c r="K47" s="132"/>
+      <c r="L47" s="132"/>
     </row>
     <row r="48" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A48" s="126"/>
-      <c r="B48" s="126"/>
-      <c r="C48" s="131" t="s">
+      <c r="A48" s="128"/>
+      <c r="B48" s="128"/>
+      <c r="C48" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="131"/>
-      <c r="E48" s="131"/>
-      <c r="F48" s="131"/>
-      <c r="G48" s="131"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
       <c r="H48" s="46">
         <f>G35+H41</f>
         <v>0</v>
       </c>
-      <c r="I48" s="132" t="s">
+      <c r="I48" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="J48" s="132"/>
-      <c r="K48" s="132"/>
-      <c r="L48" s="132"/>
+      <c r="J48" s="133"/>
+      <c r="K48" s="133"/>
+      <c r="L48" s="133"/>
     </row>
     <row r="49" spans="1:12" ht="7.5" customHeight="1">
       <c r="A49" s="11"/>
@@ -2709,7 +2695,7 @@
       <c r="L49" s="11"/>
     </row>
     <row r="50" spans="1:12" ht="24" customHeight="1">
-      <c r="A50" s="83" t="s">
+      <c r="A50" s="85" t="s">
         <v>64</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -2735,7 +2721,7 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="120" customHeight="1">
-      <c r="A51" s="83"/>
+      <c r="A51" s="85"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="6"/>
@@ -2749,7 +2735,7 @@
       <c r="L51" s="6"/>
     </row>
     <row r="52" spans="1:12" ht="24" customHeight="1">
-      <c r="A52" s="83"/>
+      <c r="A52" s="85"/>
       <c r="B52" s="7" t="s">
         <v>7</v>
       </c>
@@ -2773,32 +2759,93 @@
       </c>
     </row>
     <row r="53" spans="1:12" ht="16">
-      <c r="A53" s="125" t="s">
+      <c r="A53" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="125"/>
-      <c r="C53" s="125"/>
-      <c r="D53" s="125"/>
-      <c r="E53" s="125"/>
-      <c r="F53" s="125"/>
-      <c r="G53" s="125"/>
-      <c r="H53" s="125"/>
-      <c r="I53" s="125"/>
-      <c r="J53" s="125"/>
-      <c r="K53" s="125"/>
-      <c r="L53" s="125"/>
+      <c r="B53" s="86"/>
+      <c r="C53" s="86"/>
+      <c r="D53" s="86"/>
+      <c r="E53" s="86"/>
+      <c r="F53" s="86"/>
+      <c r="G53" s="86"/>
+      <c r="H53" s="86"/>
+      <c r="I53" s="86"/>
+      <c r="J53" s="86"/>
+      <c r="K53" s="86"/>
+      <c r="L53" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:L53"/>
-    <mergeCell ref="A46:B48"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I7"/>
+    <mergeCell ref="J5:L7"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A12:L14"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="A18:B21"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="A22:B25"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="A26:B32"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="A33:B37"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="I37:L37"/>
     <mergeCell ref="A38:B45"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="I38:L38"/>
@@ -2815,76 +2862,15 @@
     <mergeCell ref="I44:L44"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="I45:L45"/>
-    <mergeCell ref="A33:B37"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="A26:B32"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="A22:B25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="A18:B21"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A12:L14"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:B7"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I7"/>
-    <mergeCell ref="J5:L7"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:L53"/>
+    <mergeCell ref="A46:B48"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="I48:L48"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2896,9 +2882,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
@@ -2914,17 +2897,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="126" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="83" t="s">
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="85" t="s">
         <v>1</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -2939,34 +2922,34 @@
       <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" ht="120" customHeight="1">
-      <c r="A2" s="82"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="83"/>
+      <c r="A2" s="126"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="85"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="6"/>
       <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="86" t="s">
+      <c r="B3" s="119"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="86"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="83"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="85"/>
       <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
@@ -2978,198 +2961,198 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A4" s="87" t="s">
+      <c r="A4" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="86" t="s">
+      <c r="B4" s="115"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="86"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
     </row>
     <row r="5" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="91" t="s">
+      <c r="B5" s="119"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="91"/>
-      <c r="H5" s="92" t="s">
+      <c r="G5" s="121"/>
+      <c r="H5" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="92"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="123"/>
+      <c r="K5" s="123"/>
+      <c r="L5" s="123"/>
     </row>
     <row r="6" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A6" s="84"/>
-      <c r="B6" s="84"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="94"/>
+      <c r="A6" s="119"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
       <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="11"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="123"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="123"/>
     </row>
     <row r="7" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A7" s="84"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
+      <c r="A7" s="119"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="123"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="123"/>
     </row>
     <row r="8" spans="1:13" ht="7.5" customHeight="1">
       <c r="A8" s="12"/>
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A9" s="96" t="s">
+      <c r="A9" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
+      <c r="B9" s="107"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="107"/>
     </row>
     <row r="10" spans="1:13" ht="18" customHeight="1">
-      <c r="A10" s="97" t="s">
+      <c r="A10" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="97"/>
-      <c r="F10" s="97"/>
-      <c r="G10" s="97"/>
-      <c r="H10" s="97"/>
-      <c r="I10" s="97"/>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
+      <c r="B10" s="108"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="108"/>
+      <c r="G10" s="108"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
     </row>
     <row r="11" spans="1:13" ht="18" customHeight="1">
-      <c r="A11" s="98" t="s">
+      <c r="A11" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="98"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="109"/>
+      <c r="D11" s="109"/>
+      <c r="E11" s="109"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="109"/>
+      <c r="J11" s="109"/>
+      <c r="K11" s="109"/>
+      <c r="L11" s="109"/>
     </row>
     <row r="12" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A12" s="133"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="133"/>
-      <c r="I12" s="133"/>
-      <c r="J12" s="133"/>
-      <c r="K12" s="133"/>
-      <c r="L12" s="133"/>
+      <c r="A12" s="110"/>
+      <c r="B12" s="110"/>
+      <c r="C12" s="110"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="110"/>
+      <c r="L12" s="110"/>
     </row>
     <row r="13" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A13" s="133"/>
-      <c r="B13" s="133"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="133"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="133"/>
-      <c r="I13" s="133"/>
-      <c r="J13" s="133"/>
-      <c r="K13" s="133"/>
-      <c r="L13" s="133"/>
+      <c r="A13" s="110"/>
+      <c r="B13" s="110"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="110"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="110"/>
+      <c r="L13" s="110"/>
     </row>
     <row r="14" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A14" s="133"/>
-      <c r="B14" s="133"/>
-      <c r="C14" s="133"/>
-      <c r="D14" s="133"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="133"/>
-      <c r="H14" s="133"/>
-      <c r="I14" s="133"/>
-      <c r="J14" s="133"/>
-      <c r="K14" s="133"/>
-      <c r="L14" s="133"/>
+      <c r="A14" s="110"/>
+      <c r="B14" s="110"/>
+      <c r="C14" s="110"/>
+      <c r="D14" s="110"/>
+      <c r="E14" s="110"/>
+      <c r="F14" s="110"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="110"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="110"/>
+      <c r="K14" s="110"/>
+      <c r="L14" s="110"/>
     </row>
     <row r="15" spans="1:13" ht="7.5" customHeight="1">
       <c r="A15" s="12"/>
       <c r="L15" s="13"/>
     </row>
     <row r="16" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A16" s="103" t="s">
+      <c r="A16" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="103"/>
-      <c r="C16" s="101" t="s">
+      <c r="B16" s="111"/>
+      <c r="C16" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="101"/>
-      <c r="H16" s="102" t="s">
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="102"/>
-      <c r="J16" s="102"/>
-      <c r="K16" s="102"/>
-      <c r="L16" s="102"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="113"/>
     </row>
     <row r="17" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A17" s="103"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="103" t="s">
+      <c r="A17" s="111"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="103"/>
+      <c r="D17" s="111"/>
       <c r="E17" s="16" t="s">
         <v>21</v>
       </c>
@@ -3182,76 +3165,76 @@
       <c r="H17" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="I17" s="104" t="s">
+      <c r="I17" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="104"/>
-      <c r="K17" s="104"/>
-      <c r="L17" s="104"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="114"/>
     </row>
     <row r="18" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A18" s="134" t="s">
+      <c r="A18" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="134"/>
-      <c r="C18" s="135" t="s">
+      <c r="B18" s="101"/>
+      <c r="C18" s="106" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="135"/>
+      <c r="D18" s="106"/>
       <c r="E18" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F18" s="19"/>
       <c r="G18" s="20"/>
       <c r="H18" s="51"/>
-      <c r="I18" s="136"/>
-      <c r="J18" s="136"/>
-      <c r="K18" s="136"/>
-      <c r="L18" s="136"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="89"/>
+      <c r="K18" s="89"/>
+      <c r="L18" s="89"/>
     </row>
     <row r="19" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A19" s="134"/>
-      <c r="B19" s="134"/>
-      <c r="C19" s="135" t="s">
+      <c r="A19" s="101"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="135"/>
+      <c r="D19" s="106"/>
       <c r="E19" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
       <c r="H19" s="51"/>
-      <c r="I19" s="136"/>
-      <c r="J19" s="136"/>
-      <c r="K19" s="136"/>
-      <c r="L19" s="136"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="89"/>
+      <c r="K19" s="89"/>
+      <c r="L19" s="89"/>
     </row>
     <row r="20" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A20" s="134"/>
-      <c r="B20" s="134"/>
-      <c r="C20" s="135" t="s">
+      <c r="A20" s="101"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="135"/>
+      <c r="D20" s="106"/>
       <c r="E20" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
       <c r="H20" s="51"/>
-      <c r="I20" s="136"/>
-      <c r="J20" s="136"/>
-      <c r="K20" s="136"/>
-      <c r="L20" s="136"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="89"/>
+      <c r="K20" s="89"/>
+      <c r="L20" s="89"/>
     </row>
     <row r="21" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A21" s="134"/>
-      <c r="B21" s="134"/>
-      <c r="C21" s="108" t="s">
+      <c r="A21" s="101"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="108"/>
+      <c r="D21" s="91"/>
       <c r="E21" s="22"/>
       <c r="F21" s="23"/>
       <c r="G21" s="24"/>
@@ -3265,100 +3248,100 @@
       <c r="L21" s="55"/>
     </row>
     <row r="22" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A22" s="134"/>
-      <c r="B22" s="134"/>
-      <c r="C22" s="137" t="s">
+      <c r="A22" s="101"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="137"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="137"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="136"/>
-      <c r="J22" s="136"/>
-      <c r="K22" s="136"/>
-      <c r="L22" s="136"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="89"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
     </row>
     <row r="23" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A23" s="134"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="137" t="s">
+      <c r="A23" s="101"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="137"/>
-      <c r="E23" s="137"/>
-      <c r="F23" s="137"/>
-      <c r="G23" s="137"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
       <c r="H23" s="21"/>
-      <c r="I23" s="138"/>
-      <c r="J23" s="138"/>
-      <c r="K23" s="138"/>
-      <c r="L23" s="138"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="102"/>
+      <c r="K23" s="102"/>
+      <c r="L23" s="102"/>
     </row>
     <row r="24" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A24" s="139" t="s">
+      <c r="A24" s="104" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="139"/>
-      <c r="C24" s="111" t="s">
+      <c r="B24" s="104"/>
+      <c r="C24" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="111"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F24" s="26"/>
       <c r="G24" s="27"/>
       <c r="H24" s="51"/>
-      <c r="I24" s="138"/>
-      <c r="J24" s="138"/>
-      <c r="K24" s="138"/>
-      <c r="L24" s="138"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="102"/>
+      <c r="L24" s="102"/>
     </row>
     <row r="25" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A25" s="139"/>
-      <c r="B25" s="139"/>
-      <c r="C25" s="111" t="s">
+      <c r="A25" s="104"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="111"/>
+      <c r="D25" s="88"/>
       <c r="E25" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F25" s="26"/>
       <c r="G25" s="27"/>
       <c r="H25" s="51"/>
-      <c r="I25" s="138"/>
-      <c r="J25" s="138"/>
-      <c r="K25" s="138"/>
-      <c r="L25" s="138"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="102"/>
+      <c r="L25" s="102"/>
     </row>
     <row r="26" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A26" s="139"/>
-      <c r="B26" s="139"/>
-      <c r="C26" s="140" t="s">
+      <c r="A26" s="104"/>
+      <c r="B26" s="104"/>
+      <c r="C26" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="140"/>
+      <c r="D26" s="105"/>
       <c r="E26" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F26" s="26"/>
       <c r="G26" s="27"/>
       <c r="H26" s="51"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="136"/>
-      <c r="K26" s="136"/>
-      <c r="L26" s="136"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="89"/>
+      <c r="K26" s="89"/>
+      <c r="L26" s="89"/>
     </row>
     <row r="27" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A27" s="139"/>
-      <c r="B27" s="139"/>
-      <c r="C27" s="108" t="s">
+      <c r="A27" s="104"/>
+      <c r="B27" s="104"/>
+      <c r="C27" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="108"/>
+      <c r="D27" s="91"/>
       <c r="E27" s="56"/>
       <c r="F27" s="22"/>
       <c r="G27" s="24"/>
@@ -3366,54 +3349,54 @@
         <f>SUM(H24:H26)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="141"/>
-      <c r="J27" s="141"/>
-      <c r="K27" s="141"/>
-      <c r="L27" s="141"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="103"/>
+      <c r="K27" s="103"/>
+      <c r="L27" s="103"/>
     </row>
     <row r="28" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A28" s="134" t="s">
+      <c r="A28" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="134"/>
-      <c r="C28" s="106" t="s">
+      <c r="B28" s="101"/>
+      <c r="C28" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="106"/>
+      <c r="D28" s="95"/>
       <c r="E28" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="20"/>
       <c r="H28" s="51"/>
-      <c r="I28" s="136"/>
-      <c r="J28" s="136"/>
-      <c r="K28" s="136"/>
-      <c r="L28" s="136"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
+      <c r="L28" s="89"/>
     </row>
     <row r="29" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A29" s="134"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="137" t="s">
+      <c r="A29" s="101"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="92" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="137"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="137"/>
-      <c r="G29" s="137"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="92"/>
       <c r="H29" s="21"/>
-      <c r="I29" s="138"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="138"/>
-      <c r="L29" s="138"/>
+      <c r="I29" s="102"/>
+      <c r="J29" s="102"/>
+      <c r="K29" s="102"/>
+      <c r="L29" s="102"/>
     </row>
     <row r="30" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A30" s="134"/>
-      <c r="B30" s="134"/>
-      <c r="C30" s="108" t="s">
+      <c r="A30" s="101"/>
+      <c r="B30" s="101"/>
+      <c r="C30" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="108"/>
+      <c r="D30" s="91"/>
       <c r="E30" s="23"/>
       <c r="F30" s="23"/>
       <c r="G30" s="57"/>
@@ -3421,90 +3404,90 @@
         <f>SUM(H28)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="141"/>
-      <c r="J30" s="141"/>
-      <c r="K30" s="141"/>
-      <c r="L30" s="141"/>
+      <c r="I30" s="103"/>
+      <c r="J30" s="103"/>
+      <c r="K30" s="103"/>
+      <c r="L30" s="103"/>
     </row>
     <row r="31" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A31" s="142" t="s">
+      <c r="A31" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="142"/>
-      <c r="C31" s="106"/>
-      <c r="D31" s="106"/>
+      <c r="B31" s="94"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="95"/>
       <c r="E31" s="19" t="s">
         <v>77</v>
       </c>
       <c r="F31" s="19"/>
       <c r="G31" s="58"/>
       <c r="H31" s="59"/>
-      <c r="I31" s="136"/>
-      <c r="J31" s="136"/>
-      <c r="K31" s="136"/>
-      <c r="L31" s="136"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
+      <c r="L31" s="89"/>
     </row>
     <row r="32" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A32" s="142"/>
-      <c r="B32" s="142"/>
-      <c r="C32" s="143" t="s">
+      <c r="A32" s="94"/>
+      <c r="B32" s="94"/>
+      <c r="C32" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="143"/>
+      <c r="D32" s="96"/>
       <c r="E32" s="60">
         <v>0</v>
       </c>
       <c r="F32" s="26"/>
       <c r="G32" s="61"/>
       <c r="H32" s="62"/>
-      <c r="I32" s="136"/>
-      <c r="J32" s="136"/>
-      <c r="K32" s="136"/>
-      <c r="L32" s="136"/>
+      <c r="I32" s="89"/>
+      <c r="J32" s="89"/>
+      <c r="K32" s="89"/>
+      <c r="L32" s="89"/>
     </row>
     <row r="33" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A33" s="142"/>
-      <c r="B33" s="142"/>
-      <c r="C33" s="143" t="s">
+      <c r="A33" s="94"/>
+      <c r="B33" s="94"/>
+      <c r="C33" s="96" t="s">
         <v>79</v>
       </c>
-      <c r="D33" s="143"/>
+      <c r="D33" s="96"/>
       <c r="E33" s="60">
         <v>0</v>
       </c>
       <c r="F33" s="26"/>
       <c r="G33" s="61"/>
       <c r="H33" s="62"/>
-      <c r="I33" s="136"/>
-      <c r="J33" s="136"/>
-      <c r="K33" s="136"/>
-      <c r="L33" s="136"/>
+      <c r="I33" s="89"/>
+      <c r="J33" s="89"/>
+      <c r="K33" s="89"/>
+      <c r="L33" s="89"/>
     </row>
     <row r="34" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A34" s="142"/>
-      <c r="B34" s="142"/>
-      <c r="C34" s="143" t="s">
+      <c r="A34" s="94"/>
+      <c r="B34" s="94"/>
+      <c r="C34" s="96" t="s">
         <v>80</v>
       </c>
-      <c r="D34" s="143"/>
+      <c r="D34" s="96"/>
       <c r="E34" s="60">
         <v>0</v>
       </c>
       <c r="F34" s="26"/>
       <c r="G34" s="61"/>
       <c r="H34" s="62"/>
-      <c r="I34" s="136"/>
-      <c r="J34" s="136"/>
-      <c r="K34" s="136"/>
-      <c r="L34" s="136"/>
+      <c r="I34" s="89"/>
+      <c r="J34" s="89"/>
+      <c r="K34" s="89"/>
+      <c r="L34" s="89"/>
     </row>
     <row r="35" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A35" s="142"/>
-      <c r="B35" s="142"/>
-      <c r="C35" s="144" t="s">
+      <c r="A35" s="94"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="D35" s="144"/>
+      <c r="D35" s="97"/>
       <c r="E35" s="63">
         <v>0</v>
       </c>
@@ -3520,103 +3503,103 @@
       <c r="L35" s="68"/>
     </row>
     <row r="36" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A36" s="142"/>
-      <c r="B36" s="142"/>
-      <c r="C36" s="145" t="s">
+      <c r="A36" s="94"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="98" t="s">
         <v>82</v>
       </c>
-      <c r="D36" s="145"/>
-      <c r="E36" s="145"/>
-      <c r="F36" s="145"/>
-      <c r="G36" s="145"/>
+      <c r="D36" s="98"/>
+      <c r="E36" s="98"/>
+      <c r="F36" s="98"/>
+      <c r="G36" s="98"/>
       <c r="H36" s="69">
         <v>0</v>
       </c>
-      <c r="I36" s="136"/>
-      <c r="J36" s="136"/>
-      <c r="K36" s="136"/>
-      <c r="L36" s="136"/>
+      <c r="I36" s="89"/>
+      <c r="J36" s="89"/>
+      <c r="K36" s="89"/>
+      <c r="L36" s="89"/>
     </row>
     <row r="37" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A37" s="142"/>
-      <c r="B37" s="142"/>
-      <c r="C37" s="111" t="s">
+      <c r="A37" s="94"/>
+      <c r="B37" s="94"/>
+      <c r="C37" s="88" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="111"/>
+      <c r="D37" s="88"/>
       <c r="E37" s="70">
         <v>0</v>
       </c>
       <c r="F37" s="18"/>
       <c r="G37" s="71"/>
       <c r="H37" s="62"/>
-      <c r="I37" s="136"/>
-      <c r="J37" s="136"/>
-      <c r="K37" s="136"/>
-      <c r="L37" s="136"/>
+      <c r="I37" s="89"/>
+      <c r="J37" s="89"/>
+      <c r="K37" s="89"/>
+      <c r="L37" s="89"/>
     </row>
     <row r="38" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A38" s="142"/>
-      <c r="B38" s="142"/>
-      <c r="C38" s="131" t="s">
+      <c r="A38" s="94"/>
+      <c r="B38" s="94"/>
+      <c r="C38" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="D38" s="131"/>
-      <c r="E38" s="131"/>
-      <c r="F38" s="131"/>
-      <c r="G38" s="131"/>
+      <c r="D38" s="99"/>
+      <c r="E38" s="99"/>
+      <c r="F38" s="99"/>
+      <c r="G38" s="99"/>
       <c r="H38" s="80">
         <f>H35+H36+H37</f>
         <v>0</v>
       </c>
-      <c r="I38" s="146" t="s">
+      <c r="I38" s="100" t="s">
         <v>85</v>
       </c>
-      <c r="J38" s="146"/>
-      <c r="K38" s="146"/>
-      <c r="L38" s="146"/>
+      <c r="J38" s="100"/>
+      <c r="K38" s="100"/>
+      <c r="L38" s="100"/>
     </row>
     <row r="39" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A39" s="142"/>
-      <c r="B39" s="142"/>
-      <c r="C39" s="137" t="s">
+      <c r="A39" s="94"/>
+      <c r="B39" s="94"/>
+      <c r="C39" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="137"/>
-      <c r="E39" s="137"/>
-      <c r="F39" s="137"/>
-      <c r="G39" s="137"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
       <c r="H39" s="21"/>
-      <c r="I39" s="136"/>
-      <c r="J39" s="136"/>
-      <c r="K39" s="136"/>
-      <c r="L39" s="136"/>
+      <c r="I39" s="89"/>
+      <c r="J39" s="89"/>
+      <c r="K39" s="89"/>
+      <c r="L39" s="89"/>
     </row>
     <row r="40" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A40" s="142"/>
-      <c r="B40" s="142"/>
-      <c r="C40" s="147" t="s">
+      <c r="A40" s="94"/>
+      <c r="B40" s="94"/>
+      <c r="C40" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="D40" s="147"/>
-      <c r="E40" s="147"/>
-      <c r="F40" s="147"/>
-      <c r="G40" s="147"/>
+      <c r="D40" s="93"/>
+      <c r="E40" s="93"/>
+      <c r="F40" s="93"/>
+      <c r="G40" s="93"/>
       <c r="H40" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="I40" s="136"/>
-      <c r="J40" s="136"/>
-      <c r="K40" s="136"/>
-      <c r="L40" s="136"/>
+      <c r="I40" s="89"/>
+      <c r="J40" s="89"/>
+      <c r="K40" s="89"/>
+      <c r="L40" s="89"/>
     </row>
     <row r="41" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A41" s="142"/>
-      <c r="B41" s="142"/>
-      <c r="C41" s="108" t="s">
+      <c r="A41" s="94"/>
+      <c r="B41" s="94"/>
+      <c r="C41" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="108"/>
+      <c r="D41" s="91"/>
       <c r="E41" s="73"/>
       <c r="F41" s="22"/>
       <c r="G41" s="73"/>
@@ -3630,102 +3613,102 @@
       <c r="L41" s="55"/>
     </row>
     <row r="42" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A42" s="148" t="s">
+      <c r="A42" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="148"/>
-      <c r="C42" s="111" t="s">
+      <c r="B42" s="87"/>
+      <c r="C42" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="D42" s="111"/>
+      <c r="D42" s="88"/>
       <c r="E42" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="18"/>
       <c r="G42" s="27"/>
       <c r="H42" s="51"/>
-      <c r="I42" s="136"/>
-      <c r="J42" s="136"/>
-      <c r="K42" s="136"/>
-      <c r="L42" s="136"/>
+      <c r="I42" s="89"/>
+      <c r="J42" s="89"/>
+      <c r="K42" s="89"/>
+      <c r="L42" s="89"/>
     </row>
     <row r="43" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A43" s="148"/>
-      <c r="B43" s="148"/>
-      <c r="C43" s="111" t="s">
+      <c r="A43" s="87"/>
+      <c r="B43" s="87"/>
+      <c r="C43" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="111"/>
+      <c r="D43" s="88"/>
       <c r="E43" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F43" s="18"/>
       <c r="G43" s="27"/>
       <c r="H43" s="51"/>
-      <c r="I43" s="136"/>
-      <c r="J43" s="136"/>
-      <c r="K43" s="136"/>
-      <c r="L43" s="136"/>
+      <c r="I43" s="89"/>
+      <c r="J43" s="89"/>
+      <c r="K43" s="89"/>
+      <c r="L43" s="89"/>
     </row>
     <row r="44" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A44" s="148"/>
-      <c r="B44" s="148"/>
-      <c r="C44" s="111" t="s">
+      <c r="A44" s="87"/>
+      <c r="B44" s="87"/>
+      <c r="C44" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="D44" s="111"/>
+      <c r="D44" s="88"/>
       <c r="E44" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F44" s="18"/>
       <c r="G44" s="27"/>
       <c r="H44" s="51"/>
-      <c r="I44" s="136"/>
-      <c r="J44" s="136"/>
-      <c r="K44" s="136"/>
-      <c r="L44" s="136"/>
+      <c r="I44" s="89"/>
+      <c r="J44" s="89"/>
+      <c r="K44" s="89"/>
+      <c r="L44" s="89"/>
     </row>
     <row r="45" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A45" s="148"/>
-      <c r="B45" s="148"/>
-      <c r="C45" s="111" t="s">
+      <c r="A45" s="87"/>
+      <c r="B45" s="87"/>
+      <c r="C45" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="D45" s="111"/>
+      <c r="D45" s="88"/>
       <c r="E45" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F45" s="18"/>
       <c r="G45" s="27"/>
       <c r="H45" s="51"/>
-      <c r="I45" s="136"/>
-      <c r="J45" s="136"/>
-      <c r="K45" s="136"/>
-      <c r="L45" s="136"/>
+      <c r="I45" s="89"/>
+      <c r="J45" s="89"/>
+      <c r="K45" s="89"/>
+      <c r="L45" s="89"/>
     </row>
     <row r="46" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A46" s="148"/>
-      <c r="B46" s="148"/>
-      <c r="C46" s="111" t="s">
+      <c r="A46" s="87"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="88" t="s">
         <v>29</v>
       </c>
-      <c r="D46" s="111"/>
+      <c r="D46" s="88"/>
       <c r="E46" s="26"/>
       <c r="F46" s="18"/>
       <c r="G46" s="27"/>
       <c r="H46" s="51"/>
-      <c r="I46" s="149"/>
-      <c r="J46" s="149"/>
-      <c r="K46" s="149"/>
-      <c r="L46" s="149"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="90"/>
+      <c r="K46" s="90"/>
+      <c r="L46" s="90"/>
     </row>
     <row r="47" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A47" s="148"/>
-      <c r="B47" s="148"/>
-      <c r="C47" s="108" t="s">
+      <c r="A47" s="87"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="D47" s="108"/>
+      <c r="D47" s="91"/>
       <c r="E47" s="74"/>
       <c r="F47" s="75"/>
       <c r="G47" s="76"/>
@@ -3739,14 +3722,14 @@
       <c r="L47" s="55"/>
     </row>
     <row r="48" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A48" s="150" t="s">
+      <c r="A48" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="150"/>
-      <c r="C48" s="151" t="s">
+      <c r="B48" s="82"/>
+      <c r="C48" s="83" t="s">
         <v>60</v>
       </c>
-      <c r="D48" s="151"/>
+      <c r="D48" s="83"/>
       <c r="E48" s="77"/>
       <c r="F48" s="78"/>
       <c r="G48" s="43"/>
@@ -3754,10 +3737,10 @@
         <f>H21+H27+H30+H41+H47</f>
         <v>0</v>
       </c>
-      <c r="I48" s="152"/>
-      <c r="J48" s="152"/>
-      <c r="K48" s="152"/>
-      <c r="L48" s="152"/>
+      <c r="I48" s="84"/>
+      <c r="J48" s="84"/>
+      <c r="K48" s="84"/>
+      <c r="L48" s="84"/>
     </row>
     <row r="49" spans="1:12" ht="7.5" customHeight="1">
       <c r="A49" s="11"/>
@@ -3774,7 +3757,7 @@
       <c r="L49" s="11"/>
     </row>
     <row r="50" spans="1:12" ht="24" customHeight="1">
-      <c r="A50" s="83" t="s">
+      <c r="A50" s="85" t="s">
         <v>64</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -3800,7 +3783,7 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="120" customHeight="1">
-      <c r="A51" s="83"/>
+      <c r="A51" s="85"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="6"/>
@@ -3814,7 +3797,7 @@
       <c r="L51" s="6"/>
     </row>
     <row r="52" spans="1:12" ht="24" customHeight="1">
-      <c r="A52" s="83"/>
+      <c r="A52" s="85"/>
       <c r="B52" s="7" t="s">
         <v>7</v>
       </c>
@@ -3838,45 +3821,77 @@
       </c>
     </row>
     <row r="53" spans="1:12" ht="16">
-      <c r="A53" s="125" t="s">
+      <c r="A53" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="125"/>
-      <c r="C53" s="125"/>
-      <c r="D53" s="125"/>
-      <c r="E53" s="125"/>
-      <c r="F53" s="125"/>
-      <c r="G53" s="125"/>
-      <c r="H53" s="125"/>
-      <c r="I53" s="125"/>
-      <c r="J53" s="125"/>
-      <c r="K53" s="125"/>
-      <c r="L53" s="125"/>
+      <c r="B53" s="86"/>
+      <c r="C53" s="86"/>
+      <c r="D53" s="86"/>
+      <c r="E53" s="86"/>
+      <c r="F53" s="86"/>
+      <c r="G53" s="86"/>
+      <c r="H53" s="86"/>
+      <c r="I53" s="86"/>
+      <c r="J53" s="86"/>
+      <c r="K53" s="86"/>
+      <c r="L53" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:L53"/>
-    <mergeCell ref="A42:B47"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I7"/>
+    <mergeCell ref="J5:L7"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A12:L14"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="A18:B23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="A24:B27"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="A28:B30"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="I30:L30"/>
     <mergeCell ref="A31:B41"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="I31:L31"/>
@@ -3893,60 +3908,28 @@
     <mergeCell ref="I37:L37"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="I38:L38"/>
-    <mergeCell ref="A28:B30"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="A24:B27"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="A18:B23"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A12:L14"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:B7"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I7"/>
-    <mergeCell ref="J5:L7"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="A42:B47"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:L53"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/templates/trip_template.xlsx
+++ b/templates/trip_template.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parrottkim/Projects/javascript/taskflow-backend/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509DD080-CC15-C944-BD15-3EF7955ED852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF200F6-756F-1E40-8E9F-8C8EE2B3C1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18340" yWindow="500" windowWidth="32460" windowHeight="20700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9180" yWindow="21600" windowWidth="33600" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Domestic" sheetId="1" r:id="rId1"/>
     <sheet name="Overseas" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Domestic!$A$1:$L$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Domestic!$A$1:$L$55</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="96">
   <si>
     <t>국내 출장명령/정산서</t>
   </si>
@@ -174,12 +174,6 @@
   </si>
   <si>
     <t>일  비</t>
-  </si>
-  <si>
-    <t>국내-일비(공통, 임원제외)</t>
-  </si>
-  <si>
-    <t>국내-휴일특별수당(공통, 임원제외)</t>
   </si>
   <si>
     <t>가.일비는 숙박 영수증이 증빙되는 경우(1박 이상)에만 지급한다.</t>
@@ -332,6 +326,36 @@
   </si>
   <si>
     <t>현지 약물검사, 건강검진 서류 발급</t>
+  </si>
+  <si>
+    <t>기  타</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>일  비
+(공통, 임원제외)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴일 대체
+(공통, 임원제외)</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>일비</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴일·공휴일 근무 일수</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴일·공휴일 이동 일수</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -492,7 +516,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -963,6 +987,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -976,7 +1053,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1088,9 +1165,6 @@
     <xf numFmtId="179" fontId="4" fillId="6" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="6" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="179" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1223,6 +1297,240 @@
     <xf numFmtId="189" fontId="4" fillId="6" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="6" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="5" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="6" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="6" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="14" fillId="6" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1231,210 +1539,6 @@
     </xf>
     <xf numFmtId="188" fontId="15" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="6" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="14" fillId="6" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="5" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="6" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="10" fillId="6" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="6" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="5" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="5" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1530,13 +1634,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>901800</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>424080</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>3240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1798,7 +1902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" customWidth="1"/>
@@ -1812,17 +1916,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="85" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="87" t="s">
         <v>1</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -1837,34 +1941,34 @@
       <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" ht="120" customHeight="1">
-      <c r="A2" s="126"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="85"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="87"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="6"/>
       <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="117" t="s">
+      <c r="B3" s="88"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="117"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="85"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="87"/>
       <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
@@ -1876,198 +1980,198 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="115"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="117" t="s">
+      <c r="B4" s="91"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
     </row>
     <row r="5" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="121" t="s">
+      <c r="B5" s="88"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="121"/>
-      <c r="H5" s="122" t="s">
+      <c r="G5" s="95"/>
+      <c r="H5" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="122"/>
-      <c r="J5" s="123"/>
-      <c r="K5" s="123"/>
-      <c r="L5" s="123"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="97"/>
     </row>
     <row r="6" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A6" s="119"/>
-      <c r="B6" s="119"/>
-      <c r="C6" s="124"/>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
+      <c r="A6" s="88"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
       <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="11"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="123"/>
-      <c r="L6" s="123"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
     </row>
     <row r="7" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A7" s="119"/>
-      <c r="B7" s="119"/>
-      <c r="C7" s="125"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="125"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="123"/>
-      <c r="K7" s="123"/>
-      <c r="L7" s="123"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
     </row>
     <row r="8" spans="1:13" ht="7.5" customHeight="1">
       <c r="A8" s="12"/>
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A9" s="107" t="s">
+      <c r="A9" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="107"/>
-      <c r="C9" s="107"/>
-      <c r="D9" s="107"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="107"/>
-      <c r="K9" s="107"/>
-      <c r="L9" s="107"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="100"/>
+      <c r="L9" s="100"/>
     </row>
     <row r="10" spans="1:13" ht="18" customHeight="1">
-      <c r="A10" s="108" t="s">
+      <c r="A10" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="108"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="108"/>
-      <c r="L10" s="108"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="101"/>
+      <c r="I10" s="101"/>
+      <c r="J10" s="101"/>
+      <c r="K10" s="101"/>
+      <c r="L10" s="101"/>
     </row>
     <row r="11" spans="1:13" ht="18" customHeight="1">
-      <c r="A11" s="109" t="s">
+      <c r="A11" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="109"/>
-      <c r="C11" s="109"/>
-      <c r="D11" s="109"/>
-      <c r="E11" s="109"/>
-      <c r="F11" s="109"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="109"/>
-      <c r="J11" s="109"/>
-      <c r="K11" s="109"/>
-      <c r="L11" s="109"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="102"/>
+      <c r="K11" s="102"/>
+      <c r="L11" s="102"/>
     </row>
     <row r="12" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A12" s="151"/>
-      <c r="B12" s="151"/>
-      <c r="C12" s="151"/>
-      <c r="D12" s="151"/>
-      <c r="E12" s="151"/>
-      <c r="F12" s="151"/>
-      <c r="G12" s="151"/>
-      <c r="H12" s="151"/>
-      <c r="I12" s="151"/>
-      <c r="J12" s="151"/>
-      <c r="K12" s="151"/>
-      <c r="L12" s="151"/>
+      <c r="A12" s="103"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
     </row>
     <row r="13" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A13" s="151"/>
-      <c r="B13" s="151"/>
-      <c r="C13" s="151"/>
-      <c r="D13" s="151"/>
-      <c r="E13" s="151"/>
-      <c r="F13" s="151"/>
-      <c r="G13" s="151"/>
-      <c r="H13" s="151"/>
-      <c r="I13" s="151"/>
-      <c r="J13" s="151"/>
-      <c r="K13" s="151"/>
-      <c r="L13" s="151"/>
+      <c r="A13" s="103"/>
+      <c r="B13" s="103"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="103"/>
+      <c r="K13" s="103"/>
+      <c r="L13" s="103"/>
     </row>
     <row r="14" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A14" s="151"/>
-      <c r="B14" s="151"/>
-      <c r="C14" s="151"/>
-      <c r="D14" s="151"/>
-      <c r="E14" s="151"/>
-      <c r="F14" s="151"/>
-      <c r="G14" s="151"/>
-      <c r="H14" s="151"/>
-      <c r="I14" s="151"/>
-      <c r="J14" s="151"/>
-      <c r="K14" s="151"/>
-      <c r="L14" s="151"/>
+      <c r="A14" s="103"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="103"/>
+      <c r="K14" s="103"/>
+      <c r="L14" s="103"/>
     </row>
     <row r="15" spans="1:13" ht="7.5" customHeight="1">
       <c r="A15" s="12"/>
       <c r="L15" s="13"/>
     </row>
     <row r="16" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A16" s="152" t="s">
+      <c r="A16" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="152"/>
-      <c r="C16" s="112" t="s">
+      <c r="B16" s="104"/>
+      <c r="C16" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="112"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="112"/>
-      <c r="G16" s="112"/>
-      <c r="H16" s="113" t="s">
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="113"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="113"/>
-      <c r="L16" s="113"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="106"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="106"/>
     </row>
     <row r="17" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A17" s="152"/>
-      <c r="B17" s="152"/>
-      <c r="C17" s="111" t="s">
+      <c r="A17" s="104"/>
+      <c r="B17" s="104"/>
+      <c r="C17" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="111"/>
+      <c r="D17" s="107"/>
       <c r="E17" s="16" t="s">
         <v>21</v>
       </c>
@@ -2080,76 +2184,76 @@
       <c r="H17" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="114" t="s">
+      <c r="I17" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="114"/>
-      <c r="K17" s="114"/>
-      <c r="L17" s="114"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
     </row>
     <row r="18" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A18" s="145" t="s">
+      <c r="A18" s="109" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="145"/>
-      <c r="C18" s="95" t="s">
+      <c r="B18" s="109"/>
+      <c r="C18" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="95"/>
+      <c r="D18" s="110"/>
       <c r="E18" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F18" s="19"/>
       <c r="G18" s="20"/>
       <c r="H18" s="21"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="135"/>
-      <c r="L18" s="135"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
     </row>
     <row r="19" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A19" s="145"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="95" t="s">
+      <c r="A19" s="109"/>
+      <c r="B19" s="109"/>
+      <c r="C19" s="110" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="95"/>
+      <c r="D19" s="110"/>
       <c r="E19" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
       <c r="H19" s="21"/>
-      <c r="I19" s="135"/>
-      <c r="J19" s="135"/>
-      <c r="K19" s="135"/>
-      <c r="L19" s="135"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="85"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="85"/>
     </row>
     <row r="20" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="95" t="s">
+      <c r="A20" s="109"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="110" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="95"/>
+      <c r="D20" s="110"/>
       <c r="E20" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
       <c r="H20" s="21"/>
-      <c r="I20" s="135"/>
-      <c r="J20" s="135"/>
-      <c r="K20" s="135"/>
-      <c r="L20" s="135"/>
+      <c r="I20" s="84"/>
+      <c r="J20" s="85"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
     </row>
     <row r="21" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A21" s="145"/>
-      <c r="B21" s="145"/>
-      <c r="C21" s="91" t="s">
+      <c r="A21" s="109"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="111" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="91"/>
+      <c r="D21" s="111"/>
       <c r="E21" s="22"/>
       <c r="F21" s="23"/>
       <c r="G21" s="24"/>
@@ -2157,74 +2261,74 @@
         <f>SUM(H18:H20)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="141"/>
-      <c r="J21" s="141"/>
-      <c r="K21" s="141"/>
-      <c r="L21" s="141"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="112"/>
+      <c r="L21" s="112"/>
     </row>
     <row r="22" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A22" s="134" t="s">
+      <c r="A22" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="134"/>
-      <c r="C22" s="88" t="s">
+      <c r="B22" s="113"/>
+      <c r="C22" s="114" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="88"/>
+      <c r="D22" s="114"/>
       <c r="E22" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="26"/>
       <c r="G22" s="27"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="135"/>
-      <c r="J22" s="135"/>
-      <c r="K22" s="135"/>
-      <c r="L22" s="135"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="85"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
     </row>
     <row r="23" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A23" s="134"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="88" t="s">
+      <c r="A23" s="113"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="114" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="88"/>
+      <c r="D23" s="114"/>
       <c r="E23" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F23" s="26"/>
       <c r="G23" s="27"/>
       <c r="H23" s="28"/>
-      <c r="I23" s="150"/>
-      <c r="J23" s="150"/>
-      <c r="K23" s="150"/>
-      <c r="L23" s="150"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="85"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
     </row>
     <row r="24" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A24" s="134"/>
-      <c r="B24" s="134"/>
-      <c r="C24" s="88" t="s">
+      <c r="A24" s="113"/>
+      <c r="B24" s="113"/>
+      <c r="C24" s="114" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="88"/>
+      <c r="D24" s="114"/>
       <c r="E24" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F24" s="26"/>
       <c r="G24" s="27"/>
       <c r="H24" s="28"/>
-      <c r="I24" s="150"/>
-      <c r="J24" s="150"/>
-      <c r="K24" s="150"/>
-      <c r="L24" s="150"/>
+      <c r="I24" s="84"/>
+      <c r="J24" s="85"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
     </row>
     <row r="25" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A25" s="134"/>
-      <c r="B25" s="134"/>
-      <c r="C25" s="91" t="s">
+      <c r="A25" s="113"/>
+      <c r="B25" s="113"/>
+      <c r="C25" s="111" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="91"/>
+      <c r="D25" s="111"/>
       <c r="E25" s="22"/>
       <c r="F25" s="23"/>
       <c r="G25" s="24"/>
@@ -2232,20 +2336,20 @@
         <f>SUM(H22:H24)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="141"/>
-      <c r="J25" s="141"/>
-      <c r="K25" s="141"/>
-      <c r="L25" s="141"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="112"/>
     </row>
     <row r="26" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A26" s="145" t="s">
+      <c r="A26" s="109" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="145"/>
-      <c r="C26" s="95" t="s">
+      <c r="B26" s="109"/>
+      <c r="C26" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="95"/>
+      <c r="D26" s="110"/>
       <c r="E26" s="17">
         <v>70000</v>
       </c>
@@ -2257,18 +2361,18 @@
         <v>0</v>
       </c>
       <c r="H26" s="21"/>
-      <c r="I26" s="135"/>
-      <c r="J26" s="135"/>
-      <c r="K26" s="135"/>
-      <c r="L26" s="135"/>
+      <c r="I26" s="84"/>
+      <c r="J26" s="85"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="85"/>
     </row>
     <row r="27" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A27" s="145"/>
-      <c r="B27" s="145"/>
-      <c r="C27" s="95" t="s">
+      <c r="A27" s="109"/>
+      <c r="B27" s="109"/>
+      <c r="C27" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="95"/>
+      <c r="D27" s="110"/>
       <c r="E27" s="17">
         <v>60000</v>
       </c>
@@ -2280,18 +2384,18 @@
         <v>0</v>
       </c>
       <c r="H27" s="21"/>
-      <c r="I27" s="135"/>
-      <c r="J27" s="135"/>
-      <c r="K27" s="135"/>
-      <c r="L27" s="135"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
     </row>
     <row r="28" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A28" s="145"/>
-      <c r="B28" s="145"/>
-      <c r="C28" s="95" t="s">
+      <c r="A28" s="109"/>
+      <c r="B28" s="109"/>
+      <c r="C28" s="110" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="95"/>
+      <c r="D28" s="110"/>
       <c r="E28" s="17">
         <v>50000</v>
       </c>
@@ -2303,18 +2407,18 @@
         <v>0</v>
       </c>
       <c r="H28" s="21"/>
-      <c r="I28" s="135"/>
-      <c r="J28" s="135"/>
-      <c r="K28" s="135"/>
-      <c r="L28" s="135"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="85"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
     </row>
     <row r="29" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A29" s="145"/>
-      <c r="B29" s="145"/>
-      <c r="C29" s="91" t="s">
+      <c r="A29" s="109"/>
+      <c r="B29" s="109"/>
+      <c r="C29" s="111" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="91"/>
+      <c r="D29" s="111"/>
       <c r="E29" s="22"/>
       <c r="F29" s="23"/>
       <c r="G29" s="24">
@@ -2325,18 +2429,18 @@
         <f>SUM(H26:H28)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="141"/>
-      <c r="J29" s="141"/>
-      <c r="K29" s="141"/>
-      <c r="L29" s="141"/>
+      <c r="I29" s="112"/>
+      <c r="J29" s="112"/>
+      <c r="K29" s="112"/>
+      <c r="L29" s="112"/>
     </row>
     <row r="30" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A30" s="145"/>
-      <c r="B30" s="145"/>
-      <c r="C30" s="146" t="s">
+      <c r="A30" s="109"/>
+      <c r="B30" s="109"/>
+      <c r="C30" s="115" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="146"/>
+      <c r="D30" s="115"/>
       <c r="E30" s="29"/>
       <c r="F30" s="30"/>
       <c r="G30" s="31"/>
@@ -2344,406 +2448,410 @@
         <f>G29-H29</f>
         <v>0</v>
       </c>
-      <c r="I30" s="147" t="s">
+      <c r="I30" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="147"/>
-      <c r="K30" s="147"/>
-      <c r="L30" s="147"/>
+      <c r="J30" s="116"/>
+      <c r="K30" s="116"/>
+      <c r="L30" s="116"/>
     </row>
     <row r="31" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A31" s="145"/>
-      <c r="B31" s="145"/>
-      <c r="C31" s="148" t="s">
+      <c r="A31" s="109"/>
+      <c r="B31" s="109"/>
+      <c r="C31" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="148"/>
-      <c r="E31" s="148"/>
-      <c r="F31" s="148"/>
-      <c r="G31" s="148"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="117"/>
       <c r="H31" s="33"/>
-      <c r="I31" s="149"/>
-      <c r="J31" s="149"/>
-      <c r="K31" s="149"/>
-      <c r="L31" s="149"/>
+      <c r="I31" s="118"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="118"/>
+      <c r="L31" s="118"/>
     </row>
     <row r="32" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A32" s="145"/>
-      <c r="B32" s="145"/>
-      <c r="C32" s="148" t="s">
+      <c r="A32" s="109"/>
+      <c r="B32" s="109"/>
+      <c r="C32" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="148"/>
-      <c r="E32" s="148"/>
-      <c r="F32" s="148"/>
-      <c r="G32" s="148"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="117"/>
       <c r="H32" s="33"/>
-      <c r="I32" s="149"/>
-      <c r="J32" s="149"/>
-      <c r="K32" s="149"/>
-      <c r="L32" s="149"/>
+      <c r="I32" s="118"/>
+      <c r="J32" s="118"/>
+      <c r="K32" s="118"/>
+      <c r="L32" s="118"/>
     </row>
     <row r="33" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A33" s="142" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="142"/>
-      <c r="C33" s="88" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="88"/>
+      <c r="A33" s="119" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="119"/>
+      <c r="C33" s="114" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="114"/>
       <c r="E33" s="17">
         <v>35000</v>
       </c>
       <c r="F33" s="26"/>
       <c r="G33" s="34"/>
       <c r="H33" s="21"/>
-      <c r="I33" s="135"/>
-      <c r="J33" s="135"/>
-      <c r="K33" s="135"/>
-      <c r="L33" s="135"/>
+      <c r="I33" s="84"/>
+      <c r="J33" s="85"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
     </row>
     <row r="34" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A34" s="142"/>
-      <c r="B34" s="142"/>
-      <c r="C34" s="88" t="s">
+      <c r="A34" s="119"/>
+      <c r="B34" s="119"/>
+      <c r="C34" s="120" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="120"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="82">
+        <f>SUM(H33:H33)</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="121"/>
+      <c r="J34" s="121"/>
+      <c r="K34" s="121"/>
+      <c r="L34" s="121"/>
+    </row>
+    <row r="35" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A35" s="119"/>
+      <c r="B35" s="119"/>
+      <c r="C35" s="122" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="122"/>
+      <c r="E35" s="122"/>
+      <c r="F35" s="122"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="123"/>
+      <c r="J35" s="123"/>
+      <c r="K35" s="123"/>
+      <c r="L35" s="123"/>
+    </row>
+    <row r="36" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A36" s="119"/>
+      <c r="B36" s="119"/>
+      <c r="C36" s="124" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="17">
-        <v>30000</v>
-      </c>
-      <c r="F34" s="26"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="135"/>
-      <c r="J34" s="135"/>
-      <c r="K34" s="135"/>
-      <c r="L34" s="135"/>
-    </row>
-    <row r="35" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A35" s="142"/>
-      <c r="B35" s="142"/>
-      <c r="C35" s="143" t="s">
+      <c r="D36" s="124"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="124"/>
+      <c r="G36" s="124"/>
+      <c r="H36" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="I36" s="125"/>
+      <c r="J36" s="125"/>
+      <c r="K36" s="125"/>
+      <c r="L36" s="125"/>
+    </row>
+    <row r="37" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A37" s="136" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="137"/>
+      <c r="C37" s="114" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="114"/>
+      <c r="E37" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" s="26">
+        <v>0</v>
+      </c>
+      <c r="G37" s="81"/>
+      <c r="H37" s="37"/>
+      <c r="I37" s="84"/>
+      <c r="J37" s="85"/>
+      <c r="K37" s="85"/>
+      <c r="L37" s="85"/>
+    </row>
+    <row r="38" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A38" s="138"/>
+      <c r="B38" s="139"/>
+      <c r="C38" s="114" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" s="114"/>
+      <c r="E38" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38" s="26">
+        <v>0</v>
+      </c>
+      <c r="G38" s="81"/>
+      <c r="H38" s="37"/>
+      <c r="I38" s="84"/>
+      <c r="J38" s="85"/>
+      <c r="K38" s="85"/>
+      <c r="L38" s="85"/>
+    </row>
+    <row r="39" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A39" s="140"/>
+      <c r="B39" s="141"/>
+      <c r="C39" s="120" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="143"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="37">
-        <f>SUM(H33:H34)</f>
+      <c r="D39" s="120"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="83">
         <v>0</v>
       </c>
-      <c r="I35" s="144"/>
-      <c r="J35" s="144"/>
-      <c r="K35" s="144"/>
-      <c r="L35" s="144"/>
-    </row>
-    <row r="36" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A36" s="142"/>
-      <c r="B36" s="142"/>
-      <c r="C36" s="137" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="137"/>
-      <c r="E36" s="137"/>
-      <c r="F36" s="137"/>
-      <c r="G36" s="137"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="135"/>
-      <c r="J36" s="135"/>
-      <c r="K36" s="135"/>
-      <c r="L36" s="135"/>
-    </row>
-    <row r="37" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A37" s="142"/>
-      <c r="B37" s="142"/>
-      <c r="C37" s="139" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="139"/>
-      <c r="E37" s="139"/>
-      <c r="F37" s="139"/>
-      <c r="G37" s="139"/>
-      <c r="H37" s="38" t="s">
+      <c r="G39" s="36"/>
+      <c r="H39" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="I39" s="121"/>
+      <c r="J39" s="121"/>
+      <c r="K39" s="121"/>
+      <c r="L39" s="121"/>
+    </row>
+    <row r="40" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A40" s="113" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="113"/>
+      <c r="C40" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="I37" s="140"/>
-      <c r="J37" s="140"/>
-      <c r="K37" s="140"/>
-      <c r="L37" s="140"/>
-    </row>
-    <row r="38" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A38" s="134" t="s">
+      <c r="D40" s="114"/>
+      <c r="E40" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="26"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="84"/>
+      <c r="J40" s="85"/>
+      <c r="K40" s="85"/>
+      <c r="L40" s="85"/>
+    </row>
+    <row r="41" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A41" s="113"/>
+      <c r="B41" s="113"/>
+      <c r="C41" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="134"/>
-      <c r="C38" s="88" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="88"/>
-      <c r="E38" s="17" t="s">
+      <c r="D41" s="114"/>
+      <c r="E41" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F38" s="26"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="135"/>
-      <c r="J38" s="135"/>
-      <c r="K38" s="135"/>
-      <c r="L38" s="135"/>
-    </row>
-    <row r="39" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A39" s="134"/>
-      <c r="B39" s="134"/>
-      <c r="C39" s="88" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39" s="88"/>
-      <c r="E39" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="26"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="135"/>
-      <c r="J39" s="135"/>
-      <c r="K39" s="135"/>
-      <c r="L39" s="135"/>
-    </row>
-    <row r="40" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A40" s="134"/>
-      <c r="B40" s="134"/>
-      <c r="C40" s="136" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="136"/>
-      <c r="E40" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="F40" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="G40" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="H40" s="21"/>
-      <c r="I40" s="135"/>
-      <c r="J40" s="135"/>
-      <c r="K40" s="135"/>
-      <c r="L40" s="135"/>
-    </row>
-    <row r="41" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A41" s="134"/>
-      <c r="B41" s="134"/>
-      <c r="C41" s="136"/>
-      <c r="D41" s="136"/>
-      <c r="E41" s="17"/>
       <c r="F41" s="26"/>
       <c r="G41" s="27"/>
       <c r="H41" s="21"/>
-      <c r="I41" s="135"/>
-      <c r="J41" s="135"/>
-      <c r="K41" s="135"/>
-      <c r="L41" s="135"/>
+      <c r="I41" s="84"/>
+      <c r="J41" s="85"/>
+      <c r="K41" s="85"/>
+      <c r="L41" s="85"/>
     </row>
     <row r="42" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A42" s="134"/>
-      <c r="B42" s="134"/>
-      <c r="C42" s="137" t="s">
+      <c r="A42" s="113"/>
+      <c r="B42" s="113"/>
+      <c r="C42" s="126" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="126"/>
+      <c r="E42" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="H42" s="21"/>
+      <c r="I42" s="123"/>
+      <c r="J42" s="123"/>
+      <c r="K42" s="123"/>
+      <c r="L42" s="123"/>
+    </row>
+    <row r="43" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A43" s="113"/>
+      <c r="B43" s="113"/>
+      <c r="C43" s="126"/>
+      <c r="D43" s="126"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="84"/>
+      <c r="J43" s="85"/>
+      <c r="K43" s="85"/>
+      <c r="L43" s="85"/>
+    </row>
+    <row r="44" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A44" s="113"/>
+      <c r="B44" s="113"/>
+      <c r="C44" s="122" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" s="122"/>
+      <c r="E44" s="122"/>
+      <c r="F44" s="122"/>
+      <c r="G44" s="122"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="127"/>
+      <c r="J44" s="127"/>
+      <c r="K44" s="127"/>
+      <c r="L44" s="127"/>
+    </row>
+    <row r="45" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A45" s="113"/>
+      <c r="B45" s="113"/>
+      <c r="C45" s="124" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="124"/>
+      <c r="E45" s="124"/>
+      <c r="F45" s="124"/>
+      <c r="G45" s="124"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="125"/>
+      <c r="J45" s="125"/>
+      <c r="K45" s="125"/>
+      <c r="L45" s="125"/>
+    </row>
+    <row r="46" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A46" s="113"/>
+      <c r="B46" s="113"/>
+      <c r="C46" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="137"/>
-      <c r="E42" s="137"/>
-      <c r="F42" s="137"/>
-      <c r="G42" s="137"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="138"/>
-      <c r="J42" s="138"/>
-      <c r="K42" s="138"/>
-      <c r="L42" s="138"/>
-    </row>
-    <row r="43" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A43" s="134"/>
-      <c r="B43" s="134"/>
-      <c r="C43" s="139" t="s">
+      <c r="D46" s="122"/>
+      <c r="E46" s="122"/>
+      <c r="F46" s="122"/>
+      <c r="G46" s="122"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="127"/>
+      <c r="J46" s="127"/>
+      <c r="K46" s="127"/>
+      <c r="L46" s="127"/>
+    </row>
+    <row r="47" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A47" s="113"/>
+      <c r="B47" s="113"/>
+      <c r="C47" s="111" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="111"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="25">
+        <f>SUM(H40:H46)</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="112"/>
+      <c r="J47" s="112"/>
+      <c r="K47" s="112"/>
+      <c r="L47" s="112"/>
+    </row>
+    <row r="48" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A48" s="129" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="139"/>
-      <c r="E43" s="139"/>
-      <c r="F43" s="139"/>
-      <c r="G43" s="139"/>
-      <c r="H43" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="I43" s="140"/>
-      <c r="J43" s="140"/>
-      <c r="K43" s="140"/>
-      <c r="L43" s="140"/>
-    </row>
-    <row r="44" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A44" s="134"/>
-      <c r="B44" s="134"/>
-      <c r="C44" s="137" t="s">
+      <c r="B48" s="129"/>
+      <c r="C48" s="130" t="s">
         <v>58</v>
       </c>
-      <c r="D44" s="137"/>
-      <c r="E44" s="137"/>
-      <c r="F44" s="137"/>
-      <c r="G44" s="137"/>
-      <c r="H44" s="42"/>
-      <c r="I44" s="138"/>
-      <c r="J44" s="138"/>
-      <c r="K44" s="138"/>
-      <c r="L44" s="138"/>
-    </row>
-    <row r="45" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A45" s="134"/>
-      <c r="B45" s="134"/>
-      <c r="C45" s="91" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="25">
-        <f>SUM(H38:H44)</f>
+      <c r="D48" s="130"/>
+      <c r="E48" s="130"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="130"/>
+      <c r="H48" s="43">
+        <f>H21+H25+G29+G34+H47</f>
         <v>0</v>
       </c>
-      <c r="I45" s="141"/>
-      <c r="J45" s="141"/>
-      <c r="K45" s="141"/>
-      <c r="L45" s="141"/>
-    </row>
-    <row r="46" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A46" s="128" t="s">
+      <c r="I48" s="131"/>
+      <c r="J48" s="131"/>
+      <c r="K48" s="131"/>
+      <c r="L48" s="131"/>
+    </row>
+    <row r="49" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A49" s="129"/>
+      <c r="B49" s="129"/>
+      <c r="C49" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="128"/>
-      <c r="C46" s="129" t="s">
-        <v>60</v>
-      </c>
-      <c r="D46" s="129"/>
-      <c r="E46" s="129"/>
-      <c r="F46" s="129"/>
-      <c r="G46" s="129"/>
-      <c r="H46" s="44">
-        <f>H21+H25+G29+G35+H45</f>
-        <v>0</v>
-      </c>
-      <c r="I46" s="130"/>
-      <c r="J46" s="130"/>
-      <c r="K46" s="130"/>
-      <c r="L46" s="130"/>
-    </row>
-    <row r="47" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A47" s="128"/>
-      <c r="B47" s="128"/>
-      <c r="C47" s="131" t="s">
-        <v>61</v>
-      </c>
-      <c r="D47" s="131"/>
-      <c r="E47" s="131"/>
-      <c r="F47" s="131"/>
-      <c r="G47" s="131"/>
-      <c r="H47" s="45">
+      <c r="D49" s="132"/>
+      <c r="E49" s="132"/>
+      <c r="F49" s="132"/>
+      <c r="G49" s="132"/>
+      <c r="H49" s="44">
         <f>H30</f>
         <v>0</v>
       </c>
-      <c r="I47" s="132" t="s">
+      <c r="I49" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J47" s="132"/>
-      <c r="K47" s="132"/>
-      <c r="L47" s="132"/>
-    </row>
-    <row r="48" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A48" s="128"/>
-      <c r="B48" s="128"/>
-      <c r="C48" s="99" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" s="99"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="99"/>
-      <c r="H48" s="46">
-        <f>G35+H41</f>
+      <c r="J49" s="133"/>
+      <c r="K49" s="133"/>
+      <c r="L49" s="133"/>
+    </row>
+    <row r="50" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A50" s="129"/>
+      <c r="B50" s="129"/>
+      <c r="C50" s="134" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" s="134"/>
+      <c r="E50" s="134"/>
+      <c r="F50" s="134"/>
+      <c r="G50" s="134"/>
+      <c r="H50" s="45">
+        <f>G34+H43</f>
         <v>0</v>
       </c>
-      <c r="I48" s="133" t="s">
-        <v>63</v>
-      </c>
-      <c r="J48" s="133"/>
-      <c r="K48" s="133"/>
-      <c r="L48" s="133"/>
-    </row>
-    <row r="49" spans="1:12" ht="7.5" customHeight="1">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-    </row>
-    <row r="50" spans="1:12" ht="24" customHeight="1">
-      <c r="A50" s="85" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="11"/>
-      <c r="K50" s="47" t="s">
-        <v>3</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="120" customHeight="1">
-      <c r="A51" s="85"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="6"/>
+      <c r="I50" s="135" t="s">
+        <v>61</v>
+      </c>
+      <c r="J50" s="135"/>
+      <c r="K50" s="135"/>
+      <c r="L50" s="135"/>
+    </row>
+    <row r="51" spans="1:12" ht="7.5" customHeight="1">
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="11"/>
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
       <c r="J51" s="11"/>
-      <c r="K51" s="48"/>
-      <c r="L51" s="6"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
     </row>
     <row r="52" spans="1:12" ht="24" customHeight="1">
-      <c r="A52" s="85"/>
-      <c r="B52" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>7</v>
+      <c r="A52" s="87" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
@@ -2751,75 +2859,108 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
       <c r="J52" s="11"/>
-      <c r="K52" s="49" t="s">
+      <c r="K52" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="120" customHeight="1">
+      <c r="A53" s="87"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="47"/>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" spans="1:12" ht="24" customHeight="1">
+      <c r="A54" s="87"/>
+      <c r="B54" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="L52" s="9" t="s">
+      <c r="C54" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" ht="16">
-      <c r="A53" s="86" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" s="86"/>
-      <c r="C53" s="86"/>
-      <c r="D53" s="86"/>
-      <c r="E53" s="86"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="86"/>
-      <c r="H53" s="86"/>
-      <c r="I53" s="86"/>
-      <c r="J53" s="86"/>
-      <c r="K53" s="86"/>
-      <c r="L53" s="86"/>
+      <c r="D54" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="L54" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="16">
+      <c r="A55" s="128" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="128"/>
+      <c r="C55" s="128"/>
+      <c r="D55" s="128"/>
+      <c r="E55" s="128"/>
+      <c r="F55" s="128"/>
+      <c r="G55" s="128"/>
+      <c r="H55" s="128"/>
+      <c r="I55" s="128"/>
+      <c r="J55" s="128"/>
+      <c r="K55" s="128"/>
+      <c r="L55" s="128"/>
     </row>
   </sheetData>
-  <mergeCells count="95">
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:B7"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I7"/>
-    <mergeCell ref="J5:L7"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A12:L14"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="A18:B21"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="A22:B25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="I25:L25"/>
+  <mergeCells count="100">
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="A37:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="A55:L55"/>
+    <mergeCell ref="A48:B50"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="A40:B47"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D43"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="A33:B36"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="I36:L36"/>
     <mergeCell ref="A26:B32"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="I26:L26"/>
@@ -2835,42 +2976,52 @@
     <mergeCell ref="I31:L31"/>
     <mergeCell ref="C32:G32"/>
     <mergeCell ref="I32:L32"/>
-    <mergeCell ref="A33:B37"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="A38:B45"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="C40:D41"/>
+    <mergeCell ref="A22:B25"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="A18:B21"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A12:L14"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="J5:L7"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A10:L10"/>
     <mergeCell ref="I40:L40"/>
     <mergeCell ref="I41:L41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:L53"/>
-    <mergeCell ref="A46:B48"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I7"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2897,17 +3048,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1">
-      <c r="A1" s="126" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="85" t="s">
+      <c r="A1" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="87" t="s">
         <v>1</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -2922,34 +3073,34 @@
       <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" ht="120" customHeight="1">
-      <c r="A2" s="126"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="85"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="87"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="6"/>
       <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="117" t="s">
+      <c r="B3" s="88"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="117"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="85"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="87"/>
       <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
@@ -2961,198 +3112,198 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="115"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="117" t="s">
+      <c r="B4" s="91"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="93"/>
     </row>
     <row r="5" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="121" t="s">
+      <c r="B5" s="88"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="121"/>
-      <c r="H5" s="122" t="s">
+      <c r="G5" s="95"/>
+      <c r="H5" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="122"/>
-      <c r="J5" s="123"/>
-      <c r="K5" s="123"/>
-      <c r="L5" s="123"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="97"/>
     </row>
     <row r="6" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A6" s="119"/>
-      <c r="B6" s="119"/>
-      <c r="C6" s="124"/>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
+      <c r="A6" s="88"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
       <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="11"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="123"/>
-      <c r="L6" s="123"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
     </row>
     <row r="7" spans="1:13" ht="22.5" customHeight="1">
-      <c r="A7" s="119"/>
-      <c r="B7" s="119"/>
-      <c r="C7" s="125"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="125"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="125"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="123"/>
-      <c r="K7" s="123"/>
-      <c r="L7" s="123"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
     </row>
     <row r="8" spans="1:13" ht="7.5" customHeight="1">
       <c r="A8" s="12"/>
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A9" s="107" t="s">
+      <c r="A9" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="107"/>
-      <c r="C9" s="107"/>
-      <c r="D9" s="107"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="107"/>
-      <c r="K9" s="107"/>
-      <c r="L9" s="107"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="100"/>
+      <c r="L9" s="100"/>
     </row>
     <row r="10" spans="1:13" ht="18" customHeight="1">
-      <c r="A10" s="108" t="s">
+      <c r="A10" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="108"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="108"/>
-      <c r="L10" s="108"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="101"/>
+      <c r="I10" s="101"/>
+      <c r="J10" s="101"/>
+      <c r="K10" s="101"/>
+      <c r="L10" s="101"/>
     </row>
     <row r="11" spans="1:13" ht="18" customHeight="1">
-      <c r="A11" s="109" t="s">
+      <c r="A11" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="109"/>
-      <c r="C11" s="109"/>
-      <c r="D11" s="109"/>
-      <c r="E11" s="109"/>
-      <c r="F11" s="109"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="109"/>
-      <c r="J11" s="109"/>
-      <c r="K11" s="109"/>
-      <c r="L11" s="109"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="102"/>
+      <c r="K11" s="102"/>
+      <c r="L11" s="102"/>
     </row>
     <row r="12" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A12" s="110"/>
-      <c r="B12" s="110"/>
-      <c r="C12" s="110"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="110"/>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="110"/>
-      <c r="L12" s="110"/>
+      <c r="A12" s="142"/>
+      <c r="B12" s="142"/>
+      <c r="C12" s="142"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="142"/>
+      <c r="L12" s="142"/>
     </row>
     <row r="13" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A13" s="110"/>
-      <c r="B13" s="110"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="110"/>
-      <c r="L13" s="110"/>
+      <c r="A13" s="142"/>
+      <c r="B13" s="142"/>
+      <c r="C13" s="142"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="142"/>
+      <c r="F13" s="142"/>
+      <c r="G13" s="142"/>
+      <c r="H13" s="142"/>
+      <c r="I13" s="142"/>
+      <c r="J13" s="142"/>
+      <c r="K13" s="142"/>
+      <c r="L13" s="142"/>
     </row>
     <row r="14" spans="1:13" ht="28.5" customHeight="1">
-      <c r="A14" s="110"/>
-      <c r="B14" s="110"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110"/>
+      <c r="A14" s="142"/>
+      <c r="B14" s="142"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="142"/>
+      <c r="L14" s="142"/>
     </row>
     <row r="15" spans="1:13" ht="7.5" customHeight="1">
       <c r="A15" s="12"/>
       <c r="L15" s="13"/>
     </row>
     <row r="16" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A16" s="111" t="s">
+      <c r="A16" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="112" t="s">
+      <c r="B16" s="107"/>
+      <c r="C16" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="112"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="112"/>
-      <c r="G16" s="112"/>
-      <c r="H16" s="113" t="s">
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="113"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="113"/>
-      <c r="L16" s="113"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="106"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="106"/>
     </row>
     <row r="17" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A17" s="111"/>
-      <c r="B17" s="111"/>
-      <c r="C17" s="111" t="s">
+      <c r="A17" s="107"/>
+      <c r="B17" s="107"/>
+      <c r="C17" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="111"/>
+      <c r="D17" s="107"/>
       <c r="E17" s="16" t="s">
         <v>21</v>
       </c>
@@ -3160,587 +3311,587 @@
         <v>22</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="I17" s="114" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="114"/>
-      <c r="K17" s="114"/>
-      <c r="L17" s="114"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
     </row>
     <row r="18" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A18" s="101" t="s">
+      <c r="A18" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="101"/>
-      <c r="C18" s="106" t="s">
+      <c r="B18" s="143"/>
+      <c r="C18" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="106"/>
+      <c r="D18" s="144"/>
       <c r="E18" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F18" s="19"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="89"/>
-      <c r="K18" s="89"/>
-      <c r="L18" s="89"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="145"/>
+      <c r="J18" s="145"/>
+      <c r="K18" s="145"/>
+      <c r="L18" s="145"/>
     </row>
     <row r="19" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A19" s="101"/>
-      <c r="B19" s="101"/>
-      <c r="C19" s="106" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="106"/>
+      <c r="A19" s="143"/>
+      <c r="B19" s="143"/>
+      <c r="C19" s="144" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="144"/>
       <c r="E19" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F19" s="19"/>
       <c r="G19" s="20"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="89"/>
-      <c r="K19" s="89"/>
-      <c r="L19" s="89"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="145"/>
+      <c r="K19" s="145"/>
+      <c r="L19" s="145"/>
     </row>
     <row r="20" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A20" s="101"/>
-      <c r="B20" s="101"/>
-      <c r="C20" s="106" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="106"/>
+      <c r="A20" s="143"/>
+      <c r="B20" s="143"/>
+      <c r="C20" s="144" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="144"/>
       <c r="E20" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F20" s="19"/>
       <c r="G20" s="20"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="89"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+      <c r="K20" s="145"/>
+      <c r="L20" s="145"/>
     </row>
     <row r="21" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A21" s="101"/>
-      <c r="B21" s="101"/>
-      <c r="C21" s="91" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="91"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="143"/>
+      <c r="C21" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="111"/>
       <c r="E21" s="22"/>
       <c r="F21" s="23"/>
       <c r="G21" s="24"/>
-      <c r="H21" s="52">
+      <c r="H21" s="51">
         <f>SUM(H18:H20)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="53"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="55"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="54"/>
     </row>
     <row r="22" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A22" s="101"/>
-      <c r="B22" s="101"/>
-      <c r="C22" s="92" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="92"/>
+      <c r="A22" s="143"/>
+      <c r="B22" s="143"/>
+      <c r="C22" s="146" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="146"/>
+      <c r="E22" s="146"/>
+      <c r="F22" s="146"/>
+      <c r="G22" s="146"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="89"/>
-      <c r="L22" s="89"/>
+      <c r="I22" s="145"/>
+      <c r="J22" s="145"/>
+      <c r="K22" s="145"/>
+      <c r="L22" s="145"/>
     </row>
     <row r="23" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A23" s="101"/>
-      <c r="B23" s="101"/>
-      <c r="C23" s="92" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="92"/>
+      <c r="A23" s="143"/>
+      <c r="B23" s="143"/>
+      <c r="C23" s="146" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="146"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="146"/>
       <c r="H23" s="21"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="102"/>
-      <c r="K23" s="102"/>
-      <c r="L23" s="102"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="147"/>
+      <c r="K23" s="147"/>
+      <c r="L23" s="147"/>
     </row>
     <row r="24" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A24" s="104" t="s">
+      <c r="A24" s="148" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="104"/>
-      <c r="C24" s="88" t="s">
+      <c r="B24" s="148"/>
+      <c r="C24" s="114" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="88"/>
+      <c r="D24" s="114"/>
       <c r="E24" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F24" s="26"/>
       <c r="G24" s="27"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="102"/>
-      <c r="L24" s="102"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="147"/>
+      <c r="J24" s="147"/>
+      <c r="K24" s="147"/>
+      <c r="L24" s="147"/>
     </row>
     <row r="25" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A25" s="104"/>
-      <c r="B25" s="104"/>
-      <c r="C25" s="88" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="88"/>
+      <c r="A25" s="148"/>
+      <c r="B25" s="148"/>
+      <c r="C25" s="114" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="114"/>
       <c r="E25" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F25" s="26"/>
       <c r="G25" s="27"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="102"/>
-      <c r="K25" s="102"/>
-      <c r="L25" s="102"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="147"/>
+      <c r="J25" s="147"/>
+      <c r="K25" s="147"/>
+      <c r="L25" s="147"/>
     </row>
     <row r="26" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A26" s="104"/>
-      <c r="B26" s="104"/>
-      <c r="C26" s="105" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="105"/>
+      <c r="A26" s="148"/>
+      <c r="B26" s="148"/>
+      <c r="C26" s="149" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="149"/>
       <c r="E26" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F26" s="26"/>
       <c r="G26" s="27"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="89"/>
-      <c r="K26" s="89"/>
-      <c r="L26" s="89"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="145"/>
+      <c r="J26" s="145"/>
+      <c r="K26" s="145"/>
+      <c r="L26" s="145"/>
     </row>
     <row r="27" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A27" s="104"/>
-      <c r="B27" s="104"/>
-      <c r="C27" s="91" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="91"/>
-      <c r="E27" s="56"/>
+      <c r="A27" s="148"/>
+      <c r="B27" s="148"/>
+      <c r="C27" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="111"/>
+      <c r="E27" s="55"/>
       <c r="F27" s="22"/>
       <c r="G27" s="24"/>
-      <c r="H27" s="52">
+      <c r="H27" s="51">
         <f>SUM(H24:H26)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="103"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="103"/>
-      <c r="L27" s="103"/>
+      <c r="I27" s="150"/>
+      <c r="J27" s="150"/>
+      <c r="K27" s="150"/>
+      <c r="L27" s="150"/>
     </row>
     <row r="28" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A28" s="101" t="s">
+      <c r="A28" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="101"/>
-      <c r="C28" s="95" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="95"/>
+      <c r="B28" s="143"/>
+      <c r="C28" s="110" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="110"/>
       <c r="E28" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
-      <c r="L28" s="89"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="145"/>
+      <c r="J28" s="145"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="145"/>
     </row>
     <row r="29" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A29" s="101"/>
-      <c r="B29" s="101"/>
-      <c r="C29" s="92" t="s">
-        <v>76</v>
-      </c>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="92"/>
+      <c r="A29" s="143"/>
+      <c r="B29" s="143"/>
+      <c r="C29" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="146"/>
+      <c r="E29" s="146"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="146"/>
       <c r="H29" s="21"/>
-      <c r="I29" s="102"/>
-      <c r="J29" s="102"/>
-      <c r="K29" s="102"/>
-      <c r="L29" s="102"/>
+      <c r="I29" s="147"/>
+      <c r="J29" s="147"/>
+      <c r="K29" s="147"/>
+      <c r="L29" s="147"/>
     </row>
     <row r="30" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A30" s="101"/>
-      <c r="B30" s="101"/>
-      <c r="C30" s="91" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="91"/>
+      <c r="A30" s="143"/>
+      <c r="B30" s="143"/>
+      <c r="C30" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="111"/>
       <c r="E30" s="23"/>
       <c r="F30" s="23"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="52">
+      <c r="G30" s="56"/>
+      <c r="H30" s="51">
         <f>SUM(H28)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="103"/>
-      <c r="J30" s="103"/>
-      <c r="K30" s="103"/>
-      <c r="L30" s="103"/>
+      <c r="I30" s="150"/>
+      <c r="J30" s="150"/>
+      <c r="K30" s="150"/>
+      <c r="L30" s="150"/>
     </row>
     <row r="31" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A31" s="94" t="s">
+      <c r="A31" s="151" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="94"/>
-      <c r="C31" s="95"/>
-      <c r="D31" s="95"/>
+      <c r="B31" s="151"/>
+      <c r="C31" s="110"/>
+      <c r="D31" s="110"/>
       <c r="E31" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="19"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="145"/>
+      <c r="J31" s="145"/>
+      <c r="K31" s="145"/>
+      <c r="L31" s="145"/>
+    </row>
+    <row r="32" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A32" s="151"/>
+      <c r="B32" s="151"/>
+      <c r="C32" s="152" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="152"/>
+      <c r="E32" s="59">
+        <v>0</v>
+      </c>
+      <c r="F32" s="26"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="145"/>
+      <c r="J32" s="145"/>
+      <c r="K32" s="145"/>
+      <c r="L32" s="145"/>
+    </row>
+    <row r="33" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A33" s="151"/>
+      <c r="B33" s="151"/>
+      <c r="C33" s="152" t="s">
         <v>77</v>
       </c>
-      <c r="F31" s="19"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="89"/>
-      <c r="K31" s="89"/>
-      <c r="L31" s="89"/>
-    </row>
-    <row r="32" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A32" s="94"/>
-      <c r="B32" s="94"/>
-      <c r="C32" s="96" t="s">
+      <c r="D33" s="152"/>
+      <c r="E33" s="59">
+        <v>0</v>
+      </c>
+      <c r="F33" s="26"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="145"/>
+      <c r="J33" s="145"/>
+      <c r="K33" s="145"/>
+      <c r="L33" s="145"/>
+    </row>
+    <row r="34" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A34" s="151"/>
+      <c r="B34" s="151"/>
+      <c r="C34" s="152" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="96"/>
-      <c r="E32" s="60">
+      <c r="D34" s="152"/>
+      <c r="E34" s="59">
         <v>0</v>
       </c>
-      <c r="F32" s="26"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="89"/>
-      <c r="K32" s="89"/>
-      <c r="L32" s="89"/>
-    </row>
-    <row r="33" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A33" s="94"/>
-      <c r="B33" s="94"/>
-      <c r="C33" s="96" t="s">
+      <c r="F34" s="26"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="145"/>
+      <c r="J34" s="145"/>
+      <c r="K34" s="145"/>
+      <c r="L34" s="145"/>
+    </row>
+    <row r="35" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A35" s="151"/>
+      <c r="B35" s="151"/>
+      <c r="C35" s="153" t="s">
         <v>79</v>
       </c>
-      <c r="D33" s="96"/>
-      <c r="E33" s="60">
+      <c r="D35" s="153"/>
+      <c r="E35" s="62">
         <v>0</v>
       </c>
-      <c r="F33" s="26"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="62"/>
-      <c r="I33" s="89"/>
-      <c r="J33" s="89"/>
-      <c r="K33" s="89"/>
-      <c r="L33" s="89"/>
-    </row>
-    <row r="34" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A34" s="94"/>
-      <c r="B34" s="94"/>
-      <c r="C34" s="96" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="96"/>
-      <c r="E34" s="60">
-        <v>0</v>
-      </c>
-      <c r="F34" s="26"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="62"/>
-      <c r="I34" s="89"/>
-      <c r="J34" s="89"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="89"/>
-    </row>
-    <row r="35" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A35" s="94"/>
-      <c r="B35" s="94"/>
-      <c r="C35" s="97" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" s="97"/>
-      <c r="E35" s="63">
-        <v>0</v>
-      </c>
-      <c r="F35" s="64"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="81">
+      <c r="F35" s="63"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="80">
         <f>SUM(H32:H34)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="66"/>
-      <c r="J35" s="67"/>
-      <c r="K35" s="67"/>
-      <c r="L35" s="68"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="66"/>
+      <c r="K35" s="66"/>
+      <c r="L35" s="67"/>
     </row>
     <row r="36" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A36" s="94"/>
-      <c r="B36" s="94"/>
-      <c r="C36" s="98" t="s">
+      <c r="A36" s="151"/>
+      <c r="B36" s="151"/>
+      <c r="C36" s="154" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="154"/>
+      <c r="E36" s="154"/>
+      <c r="F36" s="154"/>
+      <c r="G36" s="154"/>
+      <c r="H36" s="68">
+        <v>0</v>
+      </c>
+      <c r="I36" s="145"/>
+      <c r="J36" s="145"/>
+      <c r="K36" s="145"/>
+      <c r="L36" s="145"/>
+    </row>
+    <row r="37" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A37" s="151"/>
+      <c r="B37" s="151"/>
+      <c r="C37" s="114" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="114"/>
+      <c r="E37" s="69">
+        <v>0</v>
+      </c>
+      <c r="F37" s="18"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="145"/>
+      <c r="J37" s="145"/>
+      <c r="K37" s="145"/>
+      <c r="L37" s="145"/>
+    </row>
+    <row r="38" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A38" s="151"/>
+      <c r="B38" s="151"/>
+      <c r="C38" s="134" t="s">
         <v>82</v>
       </c>
-      <c r="D36" s="98"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="98"/>
-      <c r="G36" s="98"/>
-      <c r="H36" s="69">
-        <v>0</v>
-      </c>
-      <c r="I36" s="89"/>
-      <c r="J36" s="89"/>
-      <c r="K36" s="89"/>
-      <c r="L36" s="89"/>
-    </row>
-    <row r="37" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A37" s="94"/>
-      <c r="B37" s="94"/>
-      <c r="C37" s="88" t="s">
-        <v>83</v>
-      </c>
-      <c r="D37" s="88"/>
-      <c r="E37" s="70">
-        <v>0</v>
-      </c>
-      <c r="F37" s="18"/>
-      <c r="G37" s="71"/>
-      <c r="H37" s="62"/>
-      <c r="I37" s="89"/>
-      <c r="J37" s="89"/>
-      <c r="K37" s="89"/>
-      <c r="L37" s="89"/>
-    </row>
-    <row r="38" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A38" s="94"/>
-      <c r="B38" s="94"/>
-      <c r="C38" s="99" t="s">
-        <v>84</v>
-      </c>
-      <c r="D38" s="99"/>
-      <c r="E38" s="99"/>
-      <c r="F38" s="99"/>
-      <c r="G38" s="99"/>
-      <c r="H38" s="80">
+      <c r="D38" s="134"/>
+      <c r="E38" s="134"/>
+      <c r="F38" s="134"/>
+      <c r="G38" s="134"/>
+      <c r="H38" s="79">
         <f>H35+H36+H37</f>
         <v>0</v>
       </c>
-      <c r="I38" s="100" t="s">
-        <v>85</v>
-      </c>
-      <c r="J38" s="100"/>
-      <c r="K38" s="100"/>
-      <c r="L38" s="100"/>
+      <c r="I38" s="155" t="s">
+        <v>83</v>
+      </c>
+      <c r="J38" s="155"/>
+      <c r="K38" s="155"/>
+      <c r="L38" s="155"/>
     </row>
     <row r="39" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A39" s="94"/>
-      <c r="B39" s="94"/>
-      <c r="C39" s="92" t="s">
-        <v>86</v>
-      </c>
-      <c r="D39" s="92"/>
-      <c r="E39" s="92"/>
-      <c r="F39" s="92"/>
-      <c r="G39" s="92"/>
+      <c r="A39" s="151"/>
+      <c r="B39" s="151"/>
+      <c r="C39" s="146" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" s="146"/>
+      <c r="E39" s="146"/>
+      <c r="F39" s="146"/>
+      <c r="G39" s="146"/>
       <c r="H39" s="21"/>
-      <c r="I39" s="89"/>
-      <c r="J39" s="89"/>
-      <c r="K39" s="89"/>
-      <c r="L39" s="89"/>
+      <c r="I39" s="145"/>
+      <c r="J39" s="145"/>
+      <c r="K39" s="145"/>
+      <c r="L39" s="145"/>
     </row>
     <row r="40" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A40" s="94"/>
-      <c r="B40" s="94"/>
-      <c r="C40" s="93" t="s">
-        <v>47</v>
-      </c>
-      <c r="D40" s="93"/>
-      <c r="E40" s="93"/>
-      <c r="F40" s="93"/>
-      <c r="G40" s="93"/>
-      <c r="H40" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="I40" s="89"/>
-      <c r="J40" s="89"/>
-      <c r="K40" s="89"/>
-      <c r="L40" s="89"/>
+      <c r="A40" s="151"/>
+      <c r="B40" s="151"/>
+      <c r="C40" s="156" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="156"/>
+      <c r="E40" s="156"/>
+      <c r="F40" s="156"/>
+      <c r="G40" s="156"/>
+      <c r="H40" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="I40" s="145"/>
+      <c r="J40" s="145"/>
+      <c r="K40" s="145"/>
+      <c r="L40" s="145"/>
     </row>
     <row r="41" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A41" s="94"/>
-      <c r="B41" s="94"/>
-      <c r="C41" s="91" t="s">
-        <v>70</v>
-      </c>
-      <c r="D41" s="91"/>
-      <c r="E41" s="73"/>
+      <c r="A41" s="151"/>
+      <c r="B41" s="151"/>
+      <c r="C41" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="111"/>
+      <c r="E41" s="72"/>
       <c r="F41" s="22"/>
-      <c r="G41" s="73"/>
-      <c r="H41" s="52">
+      <c r="G41" s="72"/>
+      <c r="H41" s="51">
         <f>H38*G31</f>
         <v>0</v>
       </c>
-      <c r="I41" s="53"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="55"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="54"/>
     </row>
     <row r="42" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A42" s="87" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="87"/>
-      <c r="C42" s="88" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" s="88"/>
+      <c r="A42" s="157" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="157"/>
+      <c r="C42" s="114" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" s="114"/>
       <c r="E42" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="18"/>
       <c r="G42" s="27"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="89"/>
-      <c r="J42" s="89"/>
-      <c r="K42" s="89"/>
-      <c r="L42" s="89"/>
+      <c r="H42" s="50"/>
+      <c r="I42" s="145"/>
+      <c r="J42" s="145"/>
+      <c r="K42" s="145"/>
+      <c r="L42" s="145"/>
     </row>
     <row r="43" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A43" s="87"/>
-      <c r="B43" s="87"/>
-      <c r="C43" s="88" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="88"/>
+      <c r="A43" s="157"/>
+      <c r="B43" s="157"/>
+      <c r="C43" s="114" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="114"/>
       <c r="E43" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F43" s="18"/>
       <c r="G43" s="27"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="89"/>
-      <c r="J43" s="89"/>
-      <c r="K43" s="89"/>
-      <c r="L43" s="89"/>
+      <c r="H43" s="50"/>
+      <c r="I43" s="145"/>
+      <c r="J43" s="145"/>
+      <c r="K43" s="145"/>
+      <c r="L43" s="145"/>
     </row>
     <row r="44" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A44" s="87"/>
-      <c r="B44" s="87"/>
-      <c r="C44" s="88" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" s="88"/>
+      <c r="A44" s="157"/>
+      <c r="B44" s="157"/>
+      <c r="C44" s="114" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="114"/>
       <c r="E44" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F44" s="18"/>
       <c r="G44" s="27"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="89"/>
-      <c r="J44" s="89"/>
-      <c r="K44" s="89"/>
-      <c r="L44" s="89"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="145"/>
+      <c r="J44" s="145"/>
+      <c r="K44" s="145"/>
+      <c r="L44" s="145"/>
     </row>
     <row r="45" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A45" s="87"/>
-      <c r="B45" s="87"/>
-      <c r="C45" s="88" t="s">
-        <v>90</v>
-      </c>
-      <c r="D45" s="88"/>
+      <c r="A45" s="157"/>
+      <c r="B45" s="157"/>
+      <c r="C45" s="114" t="s">
+        <v>88</v>
+      </c>
+      <c r="D45" s="114"/>
       <c r="E45" s="17" t="s">
         <v>27</v>
       </c>
       <c r="F45" s="18"/>
       <c r="G45" s="27"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="89"/>
-      <c r="J45" s="89"/>
-      <c r="K45" s="89"/>
-      <c r="L45" s="89"/>
+      <c r="H45" s="50"/>
+      <c r="I45" s="145"/>
+      <c r="J45" s="145"/>
+      <c r="K45" s="145"/>
+      <c r="L45" s="145"/>
     </row>
     <row r="46" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A46" s="87"/>
-      <c r="B46" s="87"/>
-      <c r="C46" s="88" t="s">
+      <c r="A46" s="157"/>
+      <c r="B46" s="157"/>
+      <c r="C46" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="D46" s="88"/>
+      <c r="D46" s="114"/>
       <c r="E46" s="26"/>
       <c r="F46" s="18"/>
       <c r="G46" s="27"/>
-      <c r="H46" s="51"/>
-      <c r="I46" s="90"/>
-      <c r="J46" s="90"/>
-      <c r="K46" s="90"/>
-      <c r="L46" s="90"/>
+      <c r="H46" s="50"/>
+      <c r="I46" s="158"/>
+      <c r="J46" s="158"/>
+      <c r="K46" s="158"/>
+      <c r="L46" s="158"/>
     </row>
     <row r="47" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A47" s="87"/>
-      <c r="B47" s="87"/>
-      <c r="C47" s="91" t="s">
-        <v>70</v>
-      </c>
-      <c r="D47" s="91"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="76"/>
-      <c r="H47" s="52">
+      <c r="A47" s="157"/>
+      <c r="B47" s="157"/>
+      <c r="C47" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" s="111"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="75"/>
+      <c r="H47" s="51">
         <f>SUM(H42:H46)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="53"/>
-      <c r="J47" s="54"/>
-      <c r="K47" s="54"/>
-      <c r="L47" s="55"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="53"/>
+      <c r="L47" s="54"/>
     </row>
     <row r="48" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A48" s="82" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="82"/>
-      <c r="C48" s="83" t="s">
-        <v>60</v>
-      </c>
-      <c r="D48" s="83"/>
-      <c r="E48" s="77"/>
-      <c r="F48" s="78"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="79">
+      <c r="A48" s="159" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="159"/>
+      <c r="C48" s="160" t="s">
+        <v>58</v>
+      </c>
+      <c r="D48" s="160"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="77"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="78">
         <f>H21+H27+H30+H41+H47</f>
         <v>0</v>
       </c>
-      <c r="I48" s="84"/>
-      <c r="J48" s="84"/>
-      <c r="K48" s="84"/>
-      <c r="L48" s="84"/>
+      <c r="I48" s="161"/>
+      <c r="J48" s="161"/>
+      <c r="K48" s="161"/>
+      <c r="L48" s="161"/>
     </row>
     <row r="49" spans="1:12" ht="7.5" customHeight="1">
       <c r="A49" s="11"/>
@@ -3757,8 +3908,8 @@
       <c r="L49" s="11"/>
     </row>
     <row r="50" spans="1:12" ht="24" customHeight="1">
-      <c r="A50" s="85" t="s">
-        <v>64</v>
+      <c r="A50" s="87" t="s">
+        <v>62</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>2</v>
@@ -3775,7 +3926,7 @@
       <c r="H50" s="11"/>
       <c r="I50" s="11"/>
       <c r="J50" s="11"/>
-      <c r="K50" s="47" t="s">
+      <c r="K50" s="46" t="s">
         <v>3</v>
       </c>
       <c r="L50" s="3" t="s">
@@ -3783,7 +3934,7 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="120" customHeight="1">
-      <c r="A51" s="85"/>
+      <c r="A51" s="87"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="6"/>
@@ -3793,11 +3944,11 @@
       <c r="H51" s="11"/>
       <c r="I51" s="11"/>
       <c r="J51" s="11"/>
-      <c r="K51" s="48"/>
+      <c r="K51" s="47"/>
       <c r="L51" s="6"/>
     </row>
     <row r="52" spans="1:12" ht="24" customHeight="1">
-      <c r="A52" s="85"/>
+      <c r="A52" s="87"/>
       <c r="B52" s="7" t="s">
         <v>7</v>
       </c>
@@ -3813,7 +3964,7 @@
       <c r="H52" s="11"/>
       <c r="I52" s="11"/>
       <c r="J52" s="11"/>
-      <c r="K52" s="49" t="s">
+      <c r="K52" s="48" t="s">
         <v>7</v>
       </c>
       <c r="L52" s="9" t="s">
@@ -3821,77 +3972,45 @@
       </c>
     </row>
     <row r="53" spans="1:12" ht="16">
-      <c r="A53" s="86" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" s="86"/>
-      <c r="C53" s="86"/>
-      <c r="D53" s="86"/>
-      <c r="E53" s="86"/>
-      <c r="F53" s="86"/>
-      <c r="G53" s="86"/>
-      <c r="H53" s="86"/>
-      <c r="I53" s="86"/>
-      <c r="J53" s="86"/>
-      <c r="K53" s="86"/>
-      <c r="L53" s="86"/>
+      <c r="A53" s="128" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="128"/>
+      <c r="C53" s="128"/>
+      <c r="D53" s="128"/>
+      <c r="E53" s="128"/>
+      <c r="F53" s="128"/>
+      <c r="G53" s="128"/>
+      <c r="H53" s="128"/>
+      <c r="I53" s="128"/>
+      <c r="J53" s="128"/>
+      <c r="K53" s="128"/>
+      <c r="L53" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="I1:I3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:B7"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I7"/>
-    <mergeCell ref="J5:L7"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A12:L14"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="A18:B23"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="A24:B27"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="A28:B30"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:L53"/>
+    <mergeCell ref="A42:B47"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="C41:D41"/>
     <mergeCell ref="A31:B41"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="I31:L31"/>
@@ -3908,28 +4027,60 @@
     <mergeCell ref="I37:L37"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="I38:L38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="A42:B47"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A53:L53"/>
+    <mergeCell ref="A28:B30"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="A24:B27"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="A18:B23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A12:L14"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I7"/>
+    <mergeCell ref="J5:L7"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I1:I3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
